--- a/research/traditional_assets/database/data/israel/israel_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_healthcare_support_services.xlsx
@@ -1656,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1793,22 +1793,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09906760740161943</v>
+        <v>0.09887440190459572</v>
       </c>
       <c r="C2">
-        <v>307.4988193488521</v>
+        <v>305.2974022359633</v>
       </c>
       <c r="D2">
-        <v>242.9988193488521</v>
+        <v>243.8834022359634</v>
       </c>
       <c r="E2">
-        <v>-54.7</v>
+        <v>-51.614</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.086</v>
       </c>
       <c r="G2">
         <v>64.5</v>
@@ -1829,28 +1829,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1552258</v>
       </c>
       <c r="N2">
-        <v>22.77777777777778</v>
+        <v>22.62255197777777</v>
       </c>
       <c r="O2">
-        <v>5.238888888888888</v>
+        <v>5.203186954888888</v>
       </c>
       <c r="P2">
-        <v>17.53888888888889</v>
+        <v>17.41936502288889</v>
       </c>
       <c r="Q2">
-        <v>35.53888888888889</v>
+        <v>35.41936502288889</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09906760740161943</v>
+        <v>0.09948191101474314</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8304420905045312</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.7396384993846</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1875,22 +1875,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09887440190459572</v>
+        <v>0.09868119640757197</v>
       </c>
       <c r="C3">
-        <v>305.2974022359633</v>
+        <v>303.10244890559</v>
       </c>
       <c r="D3">
-        <v>243.8834022359634</v>
+        <v>244.77444890559</v>
       </c>
       <c r="E3">
-        <v>-51.614</v>
+        <v>-48.52800000000001</v>
       </c>
       <c r="F3">
-        <v>3.086</v>
+        <v>6.172000000000001</v>
       </c>
       <c r="G3">
         <v>64.5</v>
@@ -1911,28 +1911,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M3">
-        <v>0.1552258</v>
+        <v>0.3104516</v>
       </c>
       <c r="N3">
-        <v>22.62255197777777</v>
+        <v>22.46732617777777</v>
       </c>
       <c r="O3">
-        <v>5.203186954888888</v>
+        <v>5.167485020888888</v>
       </c>
       <c r="P3">
-        <v>17.41936502288889</v>
+        <v>17.29984115688889</v>
       </c>
       <c r="Q3">
-        <v>35.41936502288889</v>
+        <v>35.29984115688889</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09948191101474314</v>
+        <v>0.09990466980364487</v>
       </c>
       <c r="T3">
-        <v>0.8304420905045312</v>
+        <v>0.8369820345154347</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.7396384993846</v>
+        <v>73.3698192496923</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1957,22 +1957,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09868119640757197</v>
+        <v>0.09848799091054826</v>
       </c>
       <c r="C4">
-        <v>303.10244890559</v>
+        <v>300.9140304653007</v>
       </c>
       <c r="D4">
-        <v>244.77444890559</v>
+        <v>245.6720304653007</v>
       </c>
       <c r="E4">
-        <v>-48.52800000000001</v>
+        <v>-45.442</v>
       </c>
       <c r="F4">
-        <v>6.172000000000001</v>
+        <v>9.258000000000001</v>
       </c>
       <c r="G4">
         <v>64.5</v>
@@ -1993,28 +1993,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M4">
-        <v>0.3104516</v>
+        <v>0.4656774</v>
       </c>
       <c r="N4">
-        <v>22.46732617777777</v>
+        <v>22.31210037777777</v>
       </c>
       <c r="O4">
-        <v>5.167485020888888</v>
+        <v>5.131783086888889</v>
       </c>
       <c r="P4">
-        <v>17.29984115688889</v>
+        <v>17.18031729088889</v>
       </c>
       <c r="Q4">
-        <v>35.29984115688889</v>
+        <v>35.18031729088889</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09990466980364487</v>
+        <v>0.1003361452686064</v>
       </c>
       <c r="T4">
-        <v>0.8369820345154347</v>
+        <v>0.8436568227327486</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.3698192496923</v>
+        <v>48.9132128331282</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09848799091054826</v>
+        <v>0.09829478541352452</v>
       </c>
       <c r="C5">
-        <v>300.9140304653007</v>
+        <v>298.7322190695016</v>
       </c>
       <c r="D5">
-        <v>245.6720304653007</v>
+        <v>246.5762190695016</v>
       </c>
       <c r="E5">
-        <v>-45.442</v>
+        <v>-42.356</v>
       </c>
       <c r="F5">
-        <v>9.258000000000001</v>
+        <v>12.344</v>
       </c>
       <c r="G5">
         <v>64.5</v>
@@ -2075,28 +2075,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M5">
-        <v>0.4656774</v>
+        <v>0.6209032</v>
       </c>
       <c r="N5">
-        <v>22.31210037777777</v>
+        <v>22.15687457777777</v>
       </c>
       <c r="O5">
-        <v>5.131783086888889</v>
+        <v>5.096081152888888</v>
       </c>
       <c r="P5">
-        <v>17.18031729088889</v>
+        <v>17.06079342488889</v>
       </c>
       <c r="Q5">
-        <v>35.18031729088889</v>
+        <v>35.06079342488889</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1003361452686064</v>
+        <v>0.1007766098057547</v>
       </c>
       <c r="T5">
-        <v>0.8436568227327486</v>
+        <v>0.8504706690379231</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.9132128331282</v>
+        <v>36.68490962484615</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2121,22 +2121,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09829478541352452</v>
+        <v>0.0981015799165008</v>
       </c>
       <c r="C6">
-        <v>298.7322190695016</v>
+        <v>296.5570879387711</v>
       </c>
       <c r="D6">
-        <v>246.5762190695016</v>
+        <v>247.4870879387711</v>
       </c>
       <c r="E6">
-        <v>-42.356</v>
+        <v>-39.27</v>
       </c>
       <c r="F6">
-        <v>12.344</v>
+        <v>15.43</v>
       </c>
       <c r="G6">
         <v>64.5</v>
@@ -2157,28 +2157,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M6">
-        <v>0.6209032</v>
+        <v>0.7761290000000001</v>
       </c>
       <c r="N6">
-        <v>22.15687457777777</v>
+        <v>22.00164877777777</v>
       </c>
       <c r="O6">
-        <v>5.096081152888888</v>
+        <v>5.060379218888889</v>
       </c>
       <c r="P6">
-        <v>17.06079342488889</v>
+        <v>16.94126955888888</v>
       </c>
       <c r="Q6">
-        <v>35.06079342488889</v>
+        <v>34.94126955888889</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1007766098057547</v>
+        <v>0.1012263472805272</v>
       </c>
       <c r="T6">
-        <v>0.8504706690379231</v>
+        <v>0.8574279647389963</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.68490962484615</v>
+        <v>29.34792769987692</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2203,22 +2203,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0981015799165008</v>
+        <v>0.09790837441947708</v>
       </c>
       <c r="C7">
-        <v>296.5570879387711</v>
+        <v>294.388711379626</v>
       </c>
       <c r="D7">
-        <v>247.4870879387711</v>
+        <v>248.4047113796261</v>
       </c>
       <c r="E7">
-        <v>-39.27</v>
+        <v>-36.184</v>
       </c>
       <c r="F7">
-        <v>15.43</v>
+        <v>18.516</v>
       </c>
       <c r="G7">
         <v>64.5</v>
@@ -2239,28 +2239,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M7">
-        <v>0.7761290000000001</v>
+        <v>0.9313548</v>
       </c>
       <c r="N7">
-        <v>22.00164877777777</v>
+        <v>21.84642297777777</v>
       </c>
       <c r="O7">
-        <v>5.060379218888889</v>
+        <v>5.024677284888888</v>
       </c>
       <c r="P7">
-        <v>16.94126955888888</v>
+        <v>16.82174569288889</v>
       </c>
       <c r="Q7">
-        <v>34.94126955888889</v>
+        <v>34.82174569288889</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1012263472805272</v>
+        <v>0.1016856536377416</v>
       </c>
       <c r="T7">
-        <v>0.8574279647389963</v>
+        <v>0.8645332880081773</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.34792769987692</v>
+        <v>24.4566064165641</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09790837441947707</v>
+        <v>0.09771516892245335</v>
       </c>
       <c r="C8">
-        <v>294.3887113796262</v>
+        <v>292.2271648047286</v>
       </c>
       <c r="D8">
-        <v>248.4047113796262</v>
+        <v>249.3291648047286</v>
       </c>
       <c r="E8">
-        <v>-36.184</v>
+        <v>-33.098</v>
       </c>
       <c r="F8">
-        <v>18.516</v>
+        <v>21.602</v>
       </c>
       <c r="G8">
         <v>64.5</v>
@@ -2321,28 +2321,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M8">
-        <v>0.9313548</v>
+        <v>1.0865806</v>
       </c>
       <c r="N8">
-        <v>21.84642297777777</v>
+        <v>21.69119717777777</v>
       </c>
       <c r="O8">
-        <v>5.024677284888888</v>
+        <v>4.988975350888889</v>
       </c>
       <c r="P8">
-        <v>16.82174569288889</v>
+        <v>16.70222182688888</v>
       </c>
       <c r="Q8">
-        <v>34.82174569288889</v>
+        <v>34.70222182688889</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1016856536377416</v>
+        <v>0.1021548375510251</v>
       </c>
       <c r="T8">
-        <v>0.8645332880081771</v>
+        <v>0.8717914139283083</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.4566064165641</v>
+        <v>20.96280549991209</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09771516892245334</v>
+        <v>0.09752196342542963</v>
       </c>
       <c r="C9">
-        <v>292.2271648047287</v>
+        <v>290.0725247535454</v>
       </c>
       <c r="D9">
-        <v>249.3291648047287</v>
+        <v>250.2605247535454</v>
       </c>
       <c r="E9">
-        <v>-33.098</v>
+        <v>-30.012</v>
       </c>
       <c r="F9">
-        <v>21.602</v>
+        <v>24.688</v>
       </c>
       <c r="G9">
         <v>64.5</v>
@@ -2403,28 +2403,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M9">
-        <v>1.0865806</v>
+        <v>1.2418064</v>
       </c>
       <c r="N9">
-        <v>21.69119717777777</v>
+        <v>21.53597137777777</v>
       </c>
       <c r="O9">
-        <v>4.988975350888889</v>
+        <v>4.953273416888888</v>
       </c>
       <c r="P9">
-        <v>16.70222182688888</v>
+        <v>16.58269796088889</v>
       </c>
       <c r="Q9">
-        <v>34.70222182688889</v>
+        <v>34.58269796088889</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1021548375510251</v>
+        <v>0.1026342211145974</v>
       </c>
       <c r="T9">
-        <v>0.8717914139283083</v>
+        <v>0.8792073251945292</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.96280549991208</v>
+        <v>18.34245481242307</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2449,22 +2449,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09752196342542963</v>
+        <v>0.09732875792840591</v>
       </c>
       <c r="C10">
-        <v>290.0725247535454</v>
+        <v>287.9248689134726</v>
       </c>
       <c r="D10">
-        <v>250.2605247535454</v>
+        <v>251.1988689134726</v>
       </c>
       <c r="E10">
-        <v>-30.012</v>
+        <v>-26.926</v>
       </c>
       <c r="F10">
-        <v>24.688</v>
+        <v>27.774</v>
       </c>
       <c r="G10">
         <v>64.5</v>
@@ -2485,28 +2485,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M10">
-        <v>1.2418064</v>
+        <v>1.3970322</v>
       </c>
       <c r="N10">
-        <v>21.53597137777777</v>
+        <v>21.38074557777777</v>
       </c>
       <c r="O10">
-        <v>4.953273416888888</v>
+        <v>4.917571482888888</v>
       </c>
       <c r="P10">
-        <v>16.58269796088889</v>
+        <v>16.46317409488888</v>
       </c>
       <c r="Q10">
-        <v>34.58269796088889</v>
+        <v>34.46317409488888</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1026342211145974</v>
+        <v>0.1031241405806658</v>
       </c>
       <c r="T10">
-        <v>0.8792073251945292</v>
+        <v>0.8867862235215462</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.34245481242307</v>
+        <v>16.3044042777094</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09732875792840591</v>
+        <v>0.09713555243138218</v>
       </c>
       <c r="C11">
-        <v>287.9248689134726</v>
+        <v>285.784276141438</v>
       </c>
       <c r="D11">
-        <v>251.1988689134726</v>
+        <v>252.144276141438</v>
       </c>
       <c r="E11">
-        <v>-26.926</v>
+        <v>-23.84</v>
       </c>
       <c r="F11">
-        <v>27.774</v>
+        <v>30.86</v>
       </c>
       <c r="G11">
         <v>64.5</v>
@@ -2567,28 +2567,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M11">
-        <v>1.3970322</v>
+        <v>1.552258</v>
       </c>
       <c r="N11">
-        <v>21.38074557777777</v>
+        <v>21.22551977777778</v>
       </c>
       <c r="O11">
-        <v>4.917571482888888</v>
+        <v>4.881869548888889</v>
       </c>
       <c r="P11">
-        <v>16.46317409488888</v>
+        <v>16.34365022888889</v>
       </c>
       <c r="Q11">
-        <v>34.46317409488888</v>
+        <v>34.34365022888889</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1031241405806658</v>
+        <v>0.1036249471459802</v>
       </c>
       <c r="T11">
-        <v>0.8867862235215462</v>
+        <v>0.8945335418113858</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.3044042777094</v>
+        <v>14.67396384993846</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2613,22 +2613,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09713555243138218</v>
+        <v>0.09694234693435846</v>
       </c>
       <c r="C12">
-        <v>285.784276141438</v>
+        <v>283.6508264859914</v>
       </c>
       <c r="D12">
-        <v>252.144276141438</v>
+        <v>253.0968264859914</v>
       </c>
       <c r="E12">
-        <v>-23.84</v>
+        <v>-20.754</v>
       </c>
       <c r="F12">
-        <v>30.86</v>
+        <v>33.94600000000001</v>
       </c>
       <c r="G12">
         <v>64.5</v>
@@ -2649,28 +2649,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M12">
-        <v>1.552258</v>
+        <v>1.7074838</v>
       </c>
       <c r="N12">
-        <v>21.22551977777778</v>
+        <v>21.07029397777778</v>
       </c>
       <c r="O12">
-        <v>4.881869548888889</v>
+        <v>4.846167614888889</v>
       </c>
       <c r="P12">
-        <v>16.34365022888889</v>
+        <v>16.22412636288889</v>
       </c>
       <c r="Q12">
-        <v>34.34365022888889</v>
+        <v>34.2241263628889</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1036249471459802</v>
+        <v>0.104137007791414</v>
       </c>
       <c r="T12">
-        <v>0.8945335418113858</v>
+        <v>0.9024549571414465</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.67396384993846</v>
+        <v>13.33996713630769</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2695,22 +2695,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09694234693435846</v>
+        <v>0.09688774143733472</v>
       </c>
       <c r="C13">
-        <v>283.6508264859914</v>
+        <v>280.8353508352104</v>
       </c>
       <c r="D13">
-        <v>253.0968264859914</v>
+        <v>253.3673508352103</v>
       </c>
       <c r="E13">
-        <v>-20.754</v>
+        <v>-17.668</v>
       </c>
       <c r="F13">
-        <v>33.94600000000001</v>
+        <v>37.032</v>
       </c>
       <c r="G13">
         <v>64.5</v>
@@ -2731,45 +2731,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M13">
-        <v>1.7074838</v>
+        <v>1.9182576</v>
       </c>
       <c r="N13">
-        <v>21.07029397777778</v>
+        <v>20.85952017777777</v>
       </c>
       <c r="O13">
-        <v>4.846167614888889</v>
+        <v>4.797689640888889</v>
       </c>
       <c r="P13">
-        <v>16.22412636288889</v>
+        <v>16.06183053688888</v>
       </c>
       <c r="Q13">
-        <v>34.2241263628889</v>
+        <v>34.06183053688889</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.104137007791414</v>
+        <v>0.1046607061787895</v>
       </c>
       <c r="T13">
-        <v>0.9024549571414465</v>
+        <v>0.9105564046380994</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.23</v>
       </c>
       <c r="W13">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.33996713630769</v>
+        <v>11.87420176402678</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2777,22 +2777,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09688774143733472</v>
+        <v>0.09670608594031101</v>
       </c>
       <c r="C14">
-        <v>280.8353508352104</v>
+        <v>278.6534779389817</v>
       </c>
       <c r="D14">
-        <v>253.3673508352103</v>
+        <v>254.2714779389817</v>
       </c>
       <c r="E14">
-        <v>-17.668</v>
+        <v>-14.582</v>
       </c>
       <c r="F14">
-        <v>37.032</v>
+        <v>40.118</v>
       </c>
       <c r="G14">
         <v>64.5</v>
@@ -2813,28 +2813,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M14">
-        <v>1.9182576</v>
+        <v>2.0781124</v>
       </c>
       <c r="N14">
-        <v>20.85952017777777</v>
+        <v>20.69966537777778</v>
       </c>
       <c r="O14">
-        <v>4.797689640888889</v>
+        <v>4.760923036888888</v>
       </c>
       <c r="P14">
-        <v>16.06183053688888</v>
+        <v>15.93874234088889</v>
       </c>
       <c r="Q14">
-        <v>34.06183053688889</v>
+        <v>33.93874234088889</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1046607061787895</v>
+        <v>0.1051964436095529</v>
       </c>
       <c r="T14">
-        <v>0.9105564046380994</v>
+        <v>0.9188440923070892</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.87420176402678</v>
+        <v>10.96080162833241</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2859,22 +2859,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09670608594031101</v>
+        <v>0.09652443044328728</v>
       </c>
       <c r="C15">
-        <v>278.6534779389817</v>
+        <v>276.4780808043132</v>
       </c>
       <c r="D15">
-        <v>254.2714779389817</v>
+        <v>255.1820808043132</v>
       </c>
       <c r="E15">
-        <v>-14.582</v>
+        <v>-11.496</v>
       </c>
       <c r="F15">
-        <v>40.118</v>
+        <v>43.20400000000001</v>
       </c>
       <c r="G15">
         <v>64.5</v>
@@ -2895,28 +2895,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M15">
-        <v>2.0781124</v>
+        <v>2.2379672</v>
       </c>
       <c r="N15">
-        <v>20.69966537777778</v>
+        <v>20.53981057777778</v>
       </c>
       <c r="O15">
-        <v>4.760923036888888</v>
+        <v>4.724156432888888</v>
       </c>
       <c r="P15">
-        <v>15.93874234088889</v>
+        <v>15.81565414488889</v>
       </c>
       <c r="Q15">
-        <v>33.93874234088889</v>
+        <v>33.81565414488889</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1051964436095529</v>
+        <v>0.105744640050334</v>
       </c>
       <c r="T15">
-        <v>0.9188440923070892</v>
+        <v>0.9273245168986137</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.96080162833241</v>
+        <v>10.17788722630867</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09652443044328728</v>
+        <v>0.09653912494626356</v>
       </c>
       <c r="C16">
-        <v>276.4780808043132</v>
+        <v>273.3181777984997</v>
       </c>
       <c r="D16">
-        <v>255.1820808043132</v>
+        <v>255.1081777984998</v>
       </c>
       <c r="E16">
-        <v>-11.496</v>
+        <v>-8.409999999999989</v>
       </c>
       <c r="F16">
-        <v>43.20400000000001</v>
+        <v>46.29000000000001</v>
       </c>
       <c r="G16">
         <v>64.5</v>
@@ -2977,45 +2977,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M16">
-        <v>2.2379672</v>
+        <v>2.476515</v>
       </c>
       <c r="N16">
-        <v>20.53981057777778</v>
+        <v>20.30126277777778</v>
       </c>
       <c r="O16">
-        <v>4.724156432888888</v>
+        <v>4.669290438888889</v>
       </c>
       <c r="P16">
-        <v>15.81565414488889</v>
+        <v>15.63197233888889</v>
       </c>
       <c r="Q16">
-        <v>33.81565414488889</v>
+        <v>33.63197233888889</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.105744640050334</v>
+        <v>0.1063057352308983</v>
       </c>
       <c r="T16">
-        <v>0.9273245168986137</v>
+        <v>0.9360044808922918</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.23</v>
       </c>
       <c r="W16">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.17788722630867</v>
+        <v>9.197512543948966</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3023,22 +3023,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09653912494626356</v>
+        <v>0.09637055944923983</v>
       </c>
       <c r="C17">
-        <v>273.3181777984997</v>
+        <v>271.0825230834591</v>
       </c>
       <c r="D17">
-        <v>255.1081777984998</v>
+        <v>255.9585230834592</v>
       </c>
       <c r="E17">
-        <v>-8.410000000000004</v>
+        <v>-5.323999999999998</v>
       </c>
       <c r="F17">
-        <v>46.29</v>
+        <v>49.376</v>
       </c>
       <c r="G17">
         <v>64.5</v>
@@ -3059,28 +3059,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M17">
-        <v>2.476515</v>
+        <v>2.641616</v>
       </c>
       <c r="N17">
-        <v>20.30126277777778</v>
+        <v>20.13616177777778</v>
       </c>
       <c r="O17">
-        <v>4.669290438888889</v>
+        <v>4.631317208888889</v>
       </c>
       <c r="P17">
-        <v>15.63197233888889</v>
+        <v>15.50484456888889</v>
       </c>
       <c r="Q17">
-        <v>33.63197233888889</v>
+        <v>33.50484456888889</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1063057352308983</v>
+        <v>0.1068801898205236</v>
       </c>
       <c r="T17">
-        <v>0.9360044808922918</v>
+        <v>0.944891110695343</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.197512543948967</v>
+        <v>8.622668009952156</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3105,22 +3105,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09637055944923983</v>
+        <v>0.0962019939522161</v>
       </c>
       <c r="C18">
-        <v>271.0825230834591</v>
+        <v>268.8525561940129</v>
       </c>
       <c r="D18">
-        <v>255.9585230834592</v>
+        <v>256.8145561940129</v>
       </c>
       <c r="E18">
-        <v>-5.323999999999998</v>
+        <v>-2.237999999999992</v>
       </c>
       <c r="F18">
-        <v>49.376</v>
+        <v>52.46200000000001</v>
       </c>
       <c r="G18">
         <v>64.5</v>
@@ -3141,28 +3141,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M18">
-        <v>2.641616</v>
+        <v>2.806717</v>
       </c>
       <c r="N18">
-        <v>20.13616177777778</v>
+        <v>19.97106077777778</v>
       </c>
       <c r="O18">
-        <v>4.631317208888889</v>
+        <v>4.593343978888889</v>
       </c>
       <c r="P18">
-        <v>15.50484456888889</v>
+        <v>15.37771679888889</v>
       </c>
       <c r="Q18">
-        <v>33.50484456888889</v>
+        <v>33.37771679888889</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1068801898205236</v>
+        <v>0.107468486689417</v>
       </c>
       <c r="T18">
-        <v>0.944891110695343</v>
+        <v>0.9539918761562991</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.622668009952156</v>
+        <v>8.115452244660851</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3187,22 +3187,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0962019939522161</v>
+        <v>0.09603342845519239</v>
       </c>
       <c r="C19">
-        <v>268.8525561940129</v>
+        <v>266.6283343891122</v>
       </c>
       <c r="D19">
-        <v>256.8145561940129</v>
+        <v>257.6763343891122</v>
       </c>
       <c r="E19">
-        <v>-2.237999999999992</v>
+        <v>0.8480000000000061</v>
       </c>
       <c r="F19">
-        <v>52.46200000000001</v>
+        <v>55.54800000000001</v>
       </c>
       <c r="G19">
         <v>64.5</v>
@@ -3223,28 +3223,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M19">
-        <v>2.806717</v>
+        <v>2.971818</v>
       </c>
       <c r="N19">
-        <v>19.97106077777778</v>
+        <v>19.80595977777778</v>
       </c>
       <c r="O19">
-        <v>4.593343978888889</v>
+        <v>4.555370748888889</v>
       </c>
       <c r="P19">
-        <v>15.37771679888889</v>
+        <v>15.25058902888889</v>
       </c>
       <c r="Q19">
-        <v>33.37771679888889</v>
+        <v>33.25058902888889</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.107468486689417</v>
+        <v>0.1080711322624297</v>
       </c>
       <c r="T19">
-        <v>0.9539918761562991</v>
+        <v>0.9633146115065468</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.115452244660851</v>
+        <v>7.664593786624138</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3269,22 +3269,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09603342845519237</v>
+        <v>0.09598190295816866</v>
       </c>
       <c r="C20">
-        <v>266.6283343891122</v>
+        <v>263.8069098718657</v>
       </c>
       <c r="D20">
-        <v>257.6763343891122</v>
+        <v>257.9409098718658</v>
       </c>
       <c r="E20">
-        <v>0.847999999999999</v>
+        <v>3.934000000000005</v>
       </c>
       <c r="F20">
-        <v>55.548</v>
+        <v>58.63400000000001</v>
       </c>
       <c r="G20">
         <v>64.5</v>
@@ -3305,45 +3305,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M20">
-        <v>2.971818</v>
+        <v>3.1838262</v>
       </c>
       <c r="N20">
-        <v>19.80595977777778</v>
+        <v>19.59395157777777</v>
       </c>
       <c r="O20">
-        <v>4.555370748888889</v>
+        <v>4.506608862888888</v>
       </c>
       <c r="P20">
-        <v>15.25058902888889</v>
+        <v>15.08734271488888</v>
       </c>
       <c r="Q20">
-        <v>33.25058902888889</v>
+        <v>33.08734271488889</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1080711322624297</v>
+        <v>0.1086886579730477</v>
       </c>
       <c r="T20">
-        <v>0.9633146115065468</v>
+        <v>0.972867537853097</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.23</v>
       </c>
       <c r="W20">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.664593786624139</v>
+        <v>7.154215194842536</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3351,22 +3351,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09598190295816866</v>
+        <v>0.09581949746114493</v>
       </c>
       <c r="C21">
-        <v>263.8069098718657</v>
+        <v>261.5584037251983</v>
       </c>
       <c r="D21">
-        <v>257.9409098718658</v>
+        <v>258.7784037251984</v>
       </c>
       <c r="E21">
-        <v>3.934000000000005</v>
+        <v>7.020000000000003</v>
       </c>
       <c r="F21">
-        <v>58.63400000000001</v>
+        <v>61.72000000000001</v>
       </c>
       <c r="G21">
         <v>64.5</v>
@@ -3387,28 +3387,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M21">
-        <v>3.1838262</v>
+        <v>3.351396</v>
       </c>
       <c r="N21">
-        <v>19.59395157777777</v>
+        <v>19.42638177777777</v>
       </c>
       <c r="O21">
-        <v>4.506608862888888</v>
+        <v>4.468067808888888</v>
       </c>
       <c r="P21">
-        <v>15.08734271488888</v>
+        <v>14.95831396888889</v>
       </c>
       <c r="Q21">
-        <v>33.08734271488889</v>
+        <v>32.95831396888889</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1086886579730477</v>
+        <v>0.1093216218264312</v>
       </c>
       <c r="T21">
-        <v>0.972867537853097</v>
+        <v>0.9826592873583109</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.154215194842536</v>
+        <v>6.79650443510041</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09581949746114493</v>
+        <v>0.09565709196412123</v>
       </c>
       <c r="C22">
-        <v>261.5584037251983</v>
+        <v>259.3153537172724</v>
       </c>
       <c r="D22">
-        <v>258.7784037251984</v>
+        <v>259.6213537172724</v>
       </c>
       <c r="E22">
-        <v>7.020000000000003</v>
+        <v>10.10600000000001</v>
       </c>
       <c r="F22">
-        <v>61.72000000000001</v>
+        <v>64.80600000000001</v>
       </c>
       <c r="G22">
         <v>64.5</v>
@@ -3469,28 +3469,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M22">
-        <v>3.351396</v>
+        <v>3.518965800000001</v>
       </c>
       <c r="N22">
-        <v>19.42638177777777</v>
+        <v>19.25881197777777</v>
       </c>
       <c r="O22">
-        <v>4.468067808888888</v>
+        <v>4.429526754888888</v>
       </c>
       <c r="P22">
-        <v>14.95831396888889</v>
+        <v>14.82928522288889</v>
       </c>
       <c r="Q22">
-        <v>32.95831396888889</v>
+        <v>32.82928522288889</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1093216218264312</v>
+        <v>0.1099706100811661</v>
       </c>
       <c r="T22">
-        <v>0.9826592873583109</v>
+        <v>0.992698929256062</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.79650443510041</v>
+        <v>6.472861366762294</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3515,22 +3515,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09565709196412123</v>
+        <v>0.09549468646709748</v>
       </c>
       <c r="C23">
-        <v>259.3153537172724</v>
+        <v>257.0778133411469</v>
       </c>
       <c r="D23">
-        <v>259.6213537172724</v>
+        <v>260.4698133411468</v>
       </c>
       <c r="E23">
-        <v>10.10599999999999</v>
+        <v>13.19200000000001</v>
       </c>
       <c r="F23">
-        <v>64.806</v>
+        <v>67.89200000000001</v>
       </c>
       <c r="G23">
         <v>64.5</v>
@@ -3551,28 +3551,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M23">
-        <v>3.5189658</v>
+        <v>3.6865356</v>
       </c>
       <c r="N23">
-        <v>19.25881197777777</v>
+        <v>19.09124217777778</v>
       </c>
       <c r="O23">
-        <v>4.429526754888888</v>
+        <v>4.390985700888889</v>
       </c>
       <c r="P23">
-        <v>14.82928522288889</v>
+        <v>14.70025647688889</v>
       </c>
       <c r="Q23">
-        <v>32.82928522288889</v>
+        <v>32.70025647688889</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1099706100811661</v>
+        <v>0.1106362390603814</v>
       </c>
       <c r="T23">
-        <v>0.992698929256062</v>
+        <v>1.00299599786914</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.472861366762295</v>
+        <v>6.178640395545827</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3597,22 +3597,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09549468646709748</v>
+        <v>0.09550938097007376</v>
       </c>
       <c r="C24">
-        <v>257.0778133411469</v>
+        <v>253.9148163161854</v>
       </c>
       <c r="D24">
-        <v>260.4698133411468</v>
+        <v>260.3928163161854</v>
       </c>
       <c r="E24">
-        <v>13.19200000000001</v>
+        <v>16.27800000000001</v>
       </c>
       <c r="F24">
-        <v>67.89200000000001</v>
+        <v>70.97800000000001</v>
       </c>
       <c r="G24">
         <v>64.5</v>
@@ -3633,45 +3633,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M24">
-        <v>3.6865356</v>
+        <v>3.925083400000001</v>
       </c>
       <c r="N24">
-        <v>19.09124217777778</v>
+        <v>18.85269437777777</v>
       </c>
       <c r="O24">
-        <v>4.390985700888889</v>
+        <v>4.336119706888888</v>
       </c>
       <c r="P24">
-        <v>14.70025647688889</v>
+        <v>14.51657467088889</v>
       </c>
       <c r="Q24">
-        <v>32.70025647688889</v>
+        <v>32.51657467088889</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1106362390603814</v>
+        <v>0.1113191571039919</v>
       </c>
       <c r="T24">
-        <v>1.00299599786914</v>
+        <v>1.01356052280983</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.178640395545827</v>
+        <v>5.803132177466031</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3679,22 +3679,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09550938097007376</v>
+        <v>0.09535467547305002</v>
       </c>
       <c r="C25">
-        <v>253.9148163161854</v>
+        <v>251.6417406202002</v>
       </c>
       <c r="D25">
-        <v>260.3928163161854</v>
+        <v>261.2057406202002</v>
       </c>
       <c r="E25">
-        <v>16.27800000000001</v>
+        <v>19.364</v>
       </c>
       <c r="F25">
-        <v>70.97800000000001</v>
+        <v>74.06400000000001</v>
       </c>
       <c r="G25">
         <v>64.5</v>
@@ -3715,28 +3715,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M25">
-        <v>3.925083400000001</v>
+        <v>4.095739200000001</v>
       </c>
       <c r="N25">
-        <v>18.85269437777777</v>
+        <v>18.68203857777777</v>
       </c>
       <c r="O25">
-        <v>4.336119706888888</v>
+        <v>4.296868872888888</v>
       </c>
       <c r="P25">
-        <v>14.51657467088889</v>
+        <v>14.38516970488889</v>
       </c>
       <c r="Q25">
-        <v>32.51657467088889</v>
+        <v>32.38516970488889</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1113191571039919</v>
+        <v>0.1120200466750658</v>
       </c>
       <c r="T25">
-        <v>1.01356052280983</v>
+        <v>1.024403061564749</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.803132177466031</v>
+        <v>5.561335003404946</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3761,22 +3761,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09535467547305002</v>
+        <v>0.09519996997602631</v>
       </c>
       <c r="C26">
-        <v>251.6417406202002</v>
+        <v>249.3737565814994</v>
       </c>
       <c r="D26">
-        <v>261.2057406202002</v>
+        <v>262.0237565814994</v>
       </c>
       <c r="E26">
-        <v>19.364</v>
+        <v>22.45</v>
       </c>
       <c r="F26">
-        <v>74.06400000000001</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="G26">
         <v>64.5</v>
@@ -3797,28 +3797,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M26">
-        <v>4.095739200000001</v>
+        <v>4.266395</v>
       </c>
       <c r="N26">
-        <v>18.68203857777777</v>
+        <v>18.51138277777778</v>
       </c>
       <c r="O26">
-        <v>4.296868872888888</v>
+        <v>4.257618038888888</v>
       </c>
       <c r="P26">
-        <v>14.38516970488889</v>
+        <v>14.25376473888889</v>
       </c>
       <c r="Q26">
-        <v>32.38516970488889</v>
+        <v>32.25376473888889</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1120200466750658</v>
+        <v>0.1127396266347017</v>
       </c>
       <c r="T26">
-        <v>1.024403061564749</v>
+        <v>1.035534734686466</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.561335003404946</v>
+        <v>5.338881603268749</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3843,22 +3843,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09519996997602631</v>
+        <v>0.09504526447900258</v>
       </c>
       <c r="C27">
-        <v>249.3737565814994</v>
+        <v>247.1109121868724</v>
       </c>
       <c r="D27">
-        <v>262.0237565814994</v>
+        <v>262.8469121868724</v>
       </c>
       <c r="E27">
-        <v>22.45</v>
+        <v>25.536</v>
       </c>
       <c r="F27">
-        <v>77.15000000000001</v>
+        <v>80.236</v>
       </c>
       <c r="G27">
         <v>64.5</v>
@@ -3879,28 +3879,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M27">
-        <v>4.266395</v>
+        <v>4.437050800000001</v>
       </c>
       <c r="N27">
-        <v>18.51138277777778</v>
+        <v>18.34072697777777</v>
       </c>
       <c r="O27">
-        <v>4.257618038888888</v>
+        <v>4.218367204888888</v>
       </c>
       <c r="P27">
-        <v>14.25376473888889</v>
+        <v>14.12235977288888</v>
       </c>
       <c r="Q27">
-        <v>32.25376473888889</v>
+        <v>32.12235977288888</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1127396266347017</v>
+        <v>0.1134786547013548</v>
       </c>
       <c r="T27">
-        <v>1.035534734686466</v>
+        <v>1.046967263838499</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.338881603268749</v>
+        <v>5.133540003143027</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3925,22 +3925,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09504526447900258</v>
+        <v>0.09489055898197886</v>
       </c>
       <c r="C28">
-        <v>247.1109121868724</v>
+        <v>244.8532560280161</v>
       </c>
       <c r="D28">
-        <v>262.8469121868724</v>
+        <v>263.6752560280161</v>
       </c>
       <c r="E28">
-        <v>25.536</v>
+        <v>28.62200000000001</v>
       </c>
       <c r="F28">
-        <v>80.236</v>
+        <v>83.32200000000002</v>
       </c>
       <c r="G28">
         <v>64.5</v>
@@ -3961,28 +3961,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M28">
-        <v>4.437050800000001</v>
+        <v>4.607706600000001</v>
       </c>
       <c r="N28">
-        <v>18.34072697777777</v>
+        <v>18.17007117777777</v>
       </c>
       <c r="O28">
-        <v>4.218367204888888</v>
+        <v>4.179116370888888</v>
       </c>
       <c r="P28">
-        <v>14.12235977288888</v>
+        <v>13.99095480688889</v>
       </c>
       <c r="Q28">
-        <v>32.12235977288888</v>
+        <v>31.99095480688889</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1134786547013548</v>
+        <v>0.1142379301122998</v>
       </c>
       <c r="T28">
-        <v>1.046967263838499</v>
+        <v>1.058713012967301</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.133540003143027</v>
+        <v>4.943408891915507</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4007,22 +4007,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09489055898197886</v>
+        <v>0.09473585348495514</v>
       </c>
       <c r="C29">
-        <v>244.8532560280161</v>
+        <v>242.6008373110974</v>
       </c>
       <c r="D29">
-        <v>263.6752560280161</v>
+        <v>264.5088373110974</v>
       </c>
       <c r="E29">
-        <v>28.62200000000001</v>
+        <v>31.70800000000001</v>
       </c>
       <c r="F29">
-        <v>83.32200000000002</v>
+        <v>86.40800000000002</v>
       </c>
       <c r="G29">
         <v>64.5</v>
@@ -4043,28 +4043,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M29">
-        <v>4.607706600000001</v>
+        <v>4.778362400000001</v>
       </c>
       <c r="N29">
-        <v>18.17007117777777</v>
+        <v>17.99941537777777</v>
       </c>
       <c r="O29">
-        <v>4.179116370888888</v>
+        <v>4.139865536888887</v>
       </c>
       <c r="P29">
-        <v>13.99095480688889</v>
+        <v>13.85954984088889</v>
       </c>
       <c r="Q29">
-        <v>31.99095480688889</v>
+        <v>31.85954984088889</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1142379301122998</v>
+        <v>0.1150182965068821</v>
       </c>
       <c r="T29">
-        <v>1.058713012967301</v>
+        <v>1.070785032905236</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.943408891915507</v>
+        <v>4.766858574347097</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4089,22 +4089,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09473585348495514</v>
+        <v>0.09458114798793141</v>
       </c>
       <c r="C30">
-        <v>242.6008373110974</v>
+        <v>240.3537058664972</v>
       </c>
       <c r="D30">
-        <v>264.5088373110974</v>
+        <v>265.3477058664972</v>
       </c>
       <c r="E30">
-        <v>31.70800000000001</v>
+        <v>34.79400000000001</v>
       </c>
       <c r="F30">
-        <v>86.40800000000002</v>
+        <v>89.49400000000001</v>
       </c>
       <c r="G30">
         <v>64.5</v>
@@ -4125,28 +4125,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M30">
-        <v>4.778362400000001</v>
+        <v>4.949018200000001</v>
       </c>
       <c r="N30">
-        <v>17.99941537777777</v>
+        <v>17.82875957777777</v>
       </c>
       <c r="O30">
-        <v>4.139865536888887</v>
+        <v>4.100614702888888</v>
       </c>
       <c r="P30">
-        <v>13.85954984088889</v>
+        <v>13.72814487488889</v>
       </c>
       <c r="Q30">
-        <v>31.85954984088889</v>
+        <v>31.72814487488889</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1150182965068821</v>
+        <v>0.1158206450534245</v>
       </c>
       <c r="T30">
-        <v>1.070785032905236</v>
+        <v>1.083197109742831</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.766858574347097</v>
+        <v>4.602484140748921</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4171,22 +4171,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09458114798793141</v>
+        <v>0.09500394249090768</v>
       </c>
       <c r="C31">
-        <v>240.3537058664972</v>
+        <v>234.9876537865557</v>
       </c>
       <c r="D31">
-        <v>265.3477058664972</v>
+        <v>263.0676537865557</v>
       </c>
       <c r="E31">
-        <v>34.794</v>
+        <v>37.88</v>
       </c>
       <c r="F31">
-        <v>89.494</v>
+        <v>92.58</v>
       </c>
       <c r="G31">
         <v>64.5</v>
@@ -4207,45 +4207,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M31">
-        <v>4.9490182</v>
+        <v>5.351124</v>
       </c>
       <c r="N31">
-        <v>17.82875957777777</v>
+        <v>17.42665377777777</v>
       </c>
       <c r="O31">
-        <v>4.100614702888888</v>
+        <v>4.008130368888888</v>
       </c>
       <c r="P31">
-        <v>13.72814487488889</v>
+        <v>13.41852340888888</v>
       </c>
       <c r="Q31">
-        <v>31.72814487488889</v>
+        <v>31.41852340888889</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1158206450534245</v>
+        <v>0.1166459178441538</v>
       </c>
       <c r="T31">
-        <v>1.083197109742831</v>
+        <v>1.095963817347215</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.23</v>
       </c>
       <c r="W31">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.602484140748921</v>
+        <v>4.256634265581917</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4253,22 +4253,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09500394249090768</v>
+        <v>0.09486848699388395</v>
       </c>
       <c r="C32">
-        <v>234.9876537865557</v>
+        <v>232.6278624385357</v>
       </c>
       <c r="D32">
-        <v>263.0676537865557</v>
+        <v>263.7938624385357</v>
       </c>
       <c r="E32">
-        <v>37.88</v>
+        <v>40.96600000000001</v>
       </c>
       <c r="F32">
-        <v>92.58</v>
+        <v>95.66600000000001</v>
       </c>
       <c r="G32">
         <v>64.5</v>
@@ -4289,28 +4289,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M32">
-        <v>5.351124</v>
+        <v>5.529494800000001</v>
       </c>
       <c r="N32">
-        <v>17.42665377777777</v>
+        <v>17.24828297777777</v>
       </c>
       <c r="O32">
-        <v>4.008130368888888</v>
+        <v>3.967105084888888</v>
       </c>
       <c r="P32">
-        <v>13.41852340888888</v>
+        <v>13.28117789288888</v>
       </c>
       <c r="Q32">
-        <v>31.41852340888889</v>
+        <v>31.28117789288889</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1166459178441538</v>
+        <v>0.1174951115853391</v>
       </c>
       <c r="T32">
-        <v>1.095963817347215</v>
+        <v>1.109100574447377</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.256634265581917</v>
+        <v>4.11932348282121</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4335,22 +4335,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09486848699388395</v>
+        <v>0.09559543149686023</v>
       </c>
       <c r="C33">
-        <v>232.6278624385357</v>
+        <v>225.6908365019361</v>
       </c>
       <c r="D33">
-        <v>263.7938624385357</v>
+        <v>259.9428365019361</v>
       </c>
       <c r="E33">
-        <v>40.96600000000001</v>
+        <v>44.05200000000001</v>
       </c>
       <c r="F33">
-        <v>95.66600000000001</v>
+        <v>98.75200000000001</v>
       </c>
       <c r="G33">
         <v>64.5</v>
@@ -4371,45 +4371,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M33">
-        <v>5.529494800000001</v>
+        <v>6.053497600000001</v>
       </c>
       <c r="N33">
-        <v>17.24828297777777</v>
+        <v>16.72428017777777</v>
       </c>
       <c r="O33">
-        <v>3.967105084888888</v>
+        <v>3.846584440888889</v>
       </c>
       <c r="P33">
-        <v>13.28117789288888</v>
+        <v>12.87769573688889</v>
       </c>
       <c r="Q33">
-        <v>31.28117789288889</v>
+        <v>30.87769573688889</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1174951115853391</v>
+        <v>0.1183692816130298</v>
       </c>
       <c r="T33">
-        <v>1.109100574447377</v>
+        <v>1.122623706756368</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.23</v>
       </c>
       <c r="W33">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.11932348282121</v>
+        <v>3.762746643820883</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4417,22 +4417,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09559543149686023</v>
+        <v>0.09548692599983651</v>
       </c>
       <c r="C34">
-        <v>225.6908365019361</v>
+        <v>223.1724954203504</v>
       </c>
       <c r="D34">
-        <v>259.9428365019361</v>
+        <v>260.5104954203504</v>
       </c>
       <c r="E34">
-        <v>44.05200000000001</v>
+        <v>47.13800000000001</v>
       </c>
       <c r="F34">
-        <v>98.75200000000001</v>
+        <v>101.838</v>
       </c>
       <c r="G34">
         <v>64.5</v>
@@ -4453,28 +4453,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M34">
-        <v>6.053497600000001</v>
+        <v>6.2426694</v>
       </c>
       <c r="N34">
-        <v>16.72428017777777</v>
+        <v>16.53510837777777</v>
       </c>
       <c r="O34">
-        <v>3.846584440888889</v>
+        <v>3.803074926888888</v>
       </c>
       <c r="P34">
-        <v>12.87769573688889</v>
+        <v>12.73203345088889</v>
       </c>
       <c r="Q34">
-        <v>30.87769573688889</v>
+        <v>30.73203345088889</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1183692816130298</v>
+        <v>0.1192695462684127</v>
       </c>
       <c r="T34">
-        <v>1.122623706756368</v>
+        <v>1.136550514656673</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.762746643820883</v>
+        <v>3.648724018250554</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09548692599983651</v>
+        <v>0.09537842050281278</v>
       </c>
       <c r="C35">
-        <v>223.1724954203504</v>
+        <v>220.6566390533828</v>
       </c>
       <c r="D35">
-        <v>260.5104954203504</v>
+        <v>261.0806390533828</v>
       </c>
       <c r="E35">
-        <v>47.13800000000001</v>
+        <v>50.22400000000002</v>
       </c>
       <c r="F35">
-        <v>101.838</v>
+        <v>104.924</v>
       </c>
       <c r="G35">
         <v>64.5</v>
@@ -4535,28 +4535,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M35">
-        <v>6.2426694</v>
+        <v>6.431841200000001</v>
       </c>
       <c r="N35">
-        <v>16.53510837777777</v>
+        <v>16.34593657777777</v>
       </c>
       <c r="O35">
-        <v>3.803074926888888</v>
+        <v>3.759565412888888</v>
       </c>
       <c r="P35">
-        <v>12.73203345088889</v>
+        <v>12.58637116488889</v>
       </c>
       <c r="Q35">
-        <v>30.73203345088889</v>
+        <v>30.58637116488889</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1192695462684127</v>
+        <v>0.1201970916709285</v>
       </c>
       <c r="T35">
-        <v>1.136550514656673</v>
+        <v>1.150899347038804</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.648724018250554</v>
+        <v>3.541408605949067</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4581,22 +4581,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09537842050281278</v>
+        <v>0.09602451500578907</v>
       </c>
       <c r="C36">
-        <v>220.6566390533828</v>
+        <v>214.2120647454679</v>
       </c>
       <c r="D36">
-        <v>261.0806390533828</v>
+        <v>257.7220647454679</v>
       </c>
       <c r="E36">
-        <v>50.22400000000002</v>
+        <v>53.31000000000002</v>
       </c>
       <c r="F36">
-        <v>104.924</v>
+        <v>108.01</v>
       </c>
       <c r="G36">
         <v>64.5</v>
@@ -4617,45 +4617,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M36">
-        <v>6.431841200000001</v>
+        <v>6.923441000000001</v>
       </c>
       <c r="N36">
-        <v>16.34593657777777</v>
+        <v>15.85433677777777</v>
       </c>
       <c r="O36">
-        <v>3.759565412888888</v>
+        <v>3.646497458888888</v>
       </c>
       <c r="P36">
-        <v>12.58637116488889</v>
+        <v>12.20783931888889</v>
       </c>
       <c r="Q36">
-        <v>30.58637116488889</v>
+        <v>30.20783931888889</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1201970916709285</v>
+        <v>0.1211531769319832</v>
       </c>
       <c r="T36">
-        <v>1.150899347038804</v>
+        <v>1.165689681955771</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.23</v>
       </c>
       <c r="W36">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.541408605949067</v>
+        <v>3.289950441951881</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4663,22 +4663,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09602451500578907</v>
+        <v>0.09593756950876534</v>
       </c>
       <c r="C37">
-        <v>214.2120647454679</v>
+        <v>211.5729905384975</v>
       </c>
       <c r="D37">
-        <v>257.7220647454679</v>
+        <v>258.1689905384975</v>
       </c>
       <c r="E37">
-        <v>53.31000000000002</v>
+        <v>56.39600000000002</v>
       </c>
       <c r="F37">
-        <v>108.01</v>
+        <v>111.096</v>
       </c>
       <c r="G37">
         <v>64.5</v>
@@ -4699,28 +4699,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M37">
-        <v>6.923441000000001</v>
+        <v>7.121253600000002</v>
       </c>
       <c r="N37">
-        <v>15.85433677777777</v>
+        <v>15.65652417777777</v>
       </c>
       <c r="O37">
-        <v>3.646497458888888</v>
+        <v>3.601000560888888</v>
       </c>
       <c r="P37">
-        <v>12.20783931888889</v>
+        <v>12.05552361688888</v>
       </c>
       <c r="Q37">
-        <v>30.20783931888889</v>
+        <v>30.05552361688889</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1211531769319832</v>
+        <v>0.1221391398574458</v>
       </c>
       <c r="T37">
-        <v>1.165689681955771</v>
+        <v>1.180942214838893</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.289950441951881</v>
+        <v>3.198562929675439</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4745,22 +4745,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09593756950876534</v>
+        <v>0.09585062401174163</v>
       </c>
       <c r="C38">
-        <v>211.5729905384975</v>
+        <v>208.9354690868011</v>
       </c>
       <c r="D38">
-        <v>258.1689905384975</v>
+        <v>258.6174690868011</v>
       </c>
       <c r="E38">
-        <v>56.396</v>
+        <v>59.482</v>
       </c>
       <c r="F38">
-        <v>111.096</v>
+        <v>114.182</v>
       </c>
       <c r="G38">
         <v>64.5</v>
@@ -4781,28 +4781,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M38">
-        <v>7.121253600000001</v>
+        <v>7.319066200000001</v>
       </c>
       <c r="N38">
-        <v>15.65652417777777</v>
+        <v>15.45871157777777</v>
       </c>
       <c r="O38">
-        <v>3.601000560888888</v>
+        <v>3.555503662888888</v>
       </c>
       <c r="P38">
-        <v>12.05552361688889</v>
+        <v>11.90320791488888</v>
       </c>
       <c r="Q38">
-        <v>30.05552361688889</v>
+        <v>29.90320791488889</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1221391398574458</v>
+        <v>0.1231564031932407</v>
       </c>
       <c r="T38">
-        <v>1.180942214838893</v>
+        <v>1.196678955115129</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.19856292967544</v>
+        <v>3.112115282927455</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4827,22 +4827,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09585062401174163</v>
+        <v>0.0957636785147179</v>
       </c>
       <c r="C39">
-        <v>208.9354690868011</v>
+        <v>206.2995084965725</v>
       </c>
       <c r="D39">
-        <v>258.6174690868011</v>
+        <v>259.0675084965725</v>
       </c>
       <c r="E39">
-        <v>59.482</v>
+        <v>62.56800000000001</v>
       </c>
       <c r="F39">
-        <v>114.182</v>
+        <v>117.268</v>
       </c>
       <c r="G39">
         <v>64.5</v>
@@ -4863,28 +4863,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M39">
-        <v>7.319066200000001</v>
+        <v>7.516878800000002</v>
       </c>
       <c r="N39">
-        <v>15.45871157777777</v>
+        <v>15.26089897777777</v>
       </c>
       <c r="O39">
-        <v>3.555503662888888</v>
+        <v>3.510006764888888</v>
       </c>
       <c r="P39">
-        <v>11.90320791488888</v>
+        <v>11.75089221288889</v>
       </c>
       <c r="Q39">
-        <v>29.90320791488889</v>
+        <v>29.75089221288889</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1231564031932407</v>
+        <v>0.1242064814753514</v>
       </c>
       <c r="T39">
-        <v>1.196678955115129</v>
+        <v>1.21292333217447</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.112115282927455</v>
+        <v>3.030217512324101</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4909,22 +4909,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0957636785147179</v>
+        <v>0.09801907301769416</v>
       </c>
       <c r="C40">
-        <v>206.2995084965725</v>
+        <v>192.0241211559558</v>
       </c>
       <c r="D40">
-        <v>259.0675084965725</v>
+        <v>247.8781211559559</v>
       </c>
       <c r="E40">
-        <v>62.56800000000001</v>
+        <v>65.65400000000001</v>
       </c>
       <c r="F40">
-        <v>117.268</v>
+        <v>120.354</v>
       </c>
       <c r="G40">
         <v>64.5</v>
@@ -4945,45 +4945,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M40">
-        <v>7.516878800000002</v>
+        <v>8.653452600000001</v>
       </c>
       <c r="N40">
-        <v>15.26089897777777</v>
+        <v>14.12432517777777</v>
       </c>
       <c r="O40">
-        <v>3.510006764888888</v>
+        <v>3.248594790888888</v>
       </c>
       <c r="P40">
-        <v>11.75089221288889</v>
+        <v>10.87573038688889</v>
       </c>
       <c r="Q40">
-        <v>29.75089221288889</v>
+        <v>28.87573038688889</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1242064814753514</v>
+        <v>0.125290988553597</v>
       </c>
       <c r="T40">
-        <v>1.21292333217447</v>
+        <v>1.229700311760347</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.23</v>
       </c>
       <c r="W40">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.030217512324101</v>
+        <v>2.632218471708942</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4991,22 +4991,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09801907301769416</v>
+        <v>0.09799218752067043</v>
       </c>
       <c r="C41">
-        <v>192.0241211559558</v>
+        <v>189.0658093561476</v>
       </c>
       <c r="D41">
-        <v>247.8781211559559</v>
+        <v>248.0058093561476</v>
       </c>
       <c r="E41">
-        <v>65.65400000000001</v>
+        <v>68.74000000000001</v>
       </c>
       <c r="F41">
-        <v>120.354</v>
+        <v>123.44</v>
       </c>
       <c r="G41">
         <v>64.5</v>
@@ -5027,28 +5027,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M41">
-        <v>8.653452600000001</v>
+        <v>8.875336000000001</v>
       </c>
       <c r="N41">
-        <v>14.12432517777777</v>
+        <v>13.90244177777777</v>
       </c>
       <c r="O41">
-        <v>3.248594790888888</v>
+        <v>3.197561608888888</v>
       </c>
       <c r="P41">
-        <v>10.87573038688889</v>
+        <v>10.70488016888889</v>
       </c>
       <c r="Q41">
-        <v>28.87573038688889</v>
+        <v>28.70488016888889</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.125290988553597</v>
+        <v>0.1264116458677841</v>
       </c>
       <c r="T41">
-        <v>1.229700311760347</v>
+        <v>1.247036523999086</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.632218471708942</v>
+        <v>2.566413009916219</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09799218752067043</v>
+        <v>0.09796530202364673</v>
       </c>
       <c r="C42">
-        <v>189.0658093561476</v>
+        <v>186.10762917489</v>
       </c>
       <c r="D42">
-        <v>248.0058093561476</v>
+        <v>248.13362917489</v>
       </c>
       <c r="E42">
-        <v>68.74000000000001</v>
+        <v>71.82600000000002</v>
       </c>
       <c r="F42">
-        <v>123.44</v>
+        <v>126.526</v>
       </c>
       <c r="G42">
         <v>64.5</v>
@@ -5109,28 +5109,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M42">
-        <v>8.875336000000001</v>
+        <v>9.097219400000002</v>
       </c>
       <c r="N42">
-        <v>13.90244177777777</v>
+        <v>13.68055837777777</v>
       </c>
       <c r="O42">
-        <v>3.197561608888888</v>
+        <v>3.146528426888888</v>
       </c>
       <c r="P42">
-        <v>10.70488016888889</v>
+        <v>10.53402995088889</v>
       </c>
       <c r="Q42">
-        <v>28.70488016888889</v>
+        <v>28.53402995088889</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1264116458677841</v>
+        <v>0.1275702915655029</v>
       </c>
       <c r="T42">
-        <v>1.247036523999086</v>
+        <v>1.264960404449309</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.566413009916219</v>
+        <v>2.503817570649969</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5155,22 +5155,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09796530202364673</v>
+        <v>0.09919967652662298</v>
       </c>
       <c r="C43">
-        <v>186.10762917489</v>
+        <v>177.2858299134143</v>
       </c>
       <c r="D43">
-        <v>248.13362917489</v>
+        <v>242.3978299134143</v>
       </c>
       <c r="E43">
-        <v>71.82600000000002</v>
+        <v>74.91200000000002</v>
       </c>
       <c r="F43">
-        <v>126.526</v>
+        <v>129.612</v>
       </c>
       <c r="G43">
         <v>64.5</v>
@@ -5191,45 +5191,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M43">
-        <v>9.097219400000002</v>
+        <v>9.824589600000003</v>
       </c>
       <c r="N43">
-        <v>13.68055837777777</v>
+        <v>12.95318817777777</v>
       </c>
       <c r="O43">
-        <v>3.146528426888888</v>
+        <v>2.979233280888888</v>
       </c>
       <c r="P43">
-        <v>10.53402995088889</v>
+        <v>9.973954896888884</v>
       </c>
       <c r="Q43">
-        <v>28.53402995088889</v>
+        <v>27.97395489688889</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1275702915655029</v>
+        <v>0.1287688905631431</v>
       </c>
       <c r="T43">
-        <v>1.264960404449309</v>
+        <v>1.283502349742642</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.23</v>
       </c>
       <c r="W43">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.503817570649969</v>
+        <v>2.318445727013144</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5237,22 +5237,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.099199676526623</v>
+        <v>0.09920282102959928</v>
       </c>
       <c r="C44">
-        <v>177.2858299134142</v>
+        <v>174.1855568715989</v>
       </c>
       <c r="D44">
-        <v>242.3978299134142</v>
+        <v>242.383556871599</v>
       </c>
       <c r="E44">
-        <v>74.91199999999999</v>
+        <v>77.998</v>
       </c>
       <c r="F44">
-        <v>129.612</v>
+        <v>132.698</v>
       </c>
       <c r="G44">
         <v>64.5</v>
@@ -5273,28 +5273,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M44">
-        <v>9.824589600000001</v>
+        <v>10.0585084</v>
       </c>
       <c r="N44">
-        <v>12.95318817777777</v>
+        <v>12.71926937777777</v>
       </c>
       <c r="O44">
-        <v>2.979233280888888</v>
+        <v>2.925431956888888</v>
       </c>
       <c r="P44">
-        <v>9.973954896888886</v>
+        <v>9.793837420888886</v>
       </c>
       <c r="Q44">
-        <v>27.97395489688889</v>
+        <v>27.79383742088889</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1287688905631431</v>
+        <v>0.1300095456659636</v>
       </c>
       <c r="T44">
-        <v>1.283502349742641</v>
+        <v>1.302694889607671</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.318445727013144</v>
+        <v>2.264528384524466</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5319,22 +5319,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09920282102959928</v>
+        <v>0.09920596553257555</v>
       </c>
       <c r="C45">
-        <v>174.1855568715989</v>
+        <v>171.0852855105556</v>
       </c>
       <c r="D45">
-        <v>242.383556871599</v>
+        <v>242.3692855105556</v>
       </c>
       <c r="E45">
-        <v>77.998</v>
+        <v>81.08400000000002</v>
       </c>
       <c r="F45">
-        <v>132.698</v>
+        <v>135.784</v>
       </c>
       <c r="G45">
         <v>64.5</v>
@@ -5355,28 +5355,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M45">
-        <v>10.0585084</v>
+        <v>10.2924272</v>
       </c>
       <c r="N45">
-        <v>12.71926937777777</v>
+        <v>12.48535057777777</v>
       </c>
       <c r="O45">
-        <v>2.925431956888888</v>
+        <v>2.871630632888888</v>
       </c>
       <c r="P45">
-        <v>9.793837420888886</v>
+        <v>9.613719944888885</v>
       </c>
       <c r="Q45">
-        <v>27.79383742088889</v>
+        <v>27.61371994488889</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1300095456659636</v>
+        <v>0.1312945098795992</v>
       </c>
       <c r="T45">
-        <v>1.302694889607671</v>
+        <v>1.322572877325022</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.264528384524466</v>
+        <v>2.213061830330728</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5401,22 +5401,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09920596553257555</v>
+        <v>0.09920911003555181</v>
       </c>
       <c r="C46">
-        <v>171.0852855105556</v>
+        <v>167.9850158299874</v>
       </c>
       <c r="D46">
-        <v>242.3692855105556</v>
+        <v>242.3550158299874</v>
       </c>
       <c r="E46">
-        <v>81.08400000000002</v>
+        <v>84.17</v>
       </c>
       <c r="F46">
-        <v>135.784</v>
+        <v>138.87</v>
       </c>
       <c r="G46">
         <v>64.5</v>
@@ -5437,28 +5437,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M46">
-        <v>10.2924272</v>
+        <v>10.526346</v>
       </c>
       <c r="N46">
-        <v>12.48535057777777</v>
+        <v>12.25143177777777</v>
       </c>
       <c r="O46">
-        <v>2.871630632888888</v>
+        <v>2.817829308888888</v>
       </c>
       <c r="P46">
-        <v>9.613719944888885</v>
+        <v>9.433602468888886</v>
       </c>
       <c r="Q46">
-        <v>27.61371994488889</v>
+        <v>27.43360246888889</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1312945098795992</v>
+        <v>0.1326262000646397</v>
       </c>
       <c r="T46">
-        <v>1.322572877325022</v>
+        <v>1.343173700959368</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.213061830330728</v>
+        <v>2.163882678545601</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5483,22 +5483,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09920911003555181</v>
+        <v>0.09921225453852811</v>
       </c>
       <c r="C47">
-        <v>167.9850158299874</v>
+        <v>164.8847478295971</v>
       </c>
       <c r="D47">
-        <v>242.3550158299874</v>
+        <v>242.3407478295971</v>
       </c>
       <c r="E47">
-        <v>84.17</v>
+        <v>87.25600000000001</v>
       </c>
       <c r="F47">
-        <v>138.87</v>
+        <v>141.956</v>
       </c>
       <c r="G47">
         <v>64.5</v>
@@ -5519,28 +5519,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M47">
-        <v>10.526346</v>
+        <v>10.7602648</v>
       </c>
       <c r="N47">
-        <v>12.25143177777777</v>
+        <v>12.01751297777777</v>
       </c>
       <c r="O47">
-        <v>2.817829308888888</v>
+        <v>2.764027984888888</v>
       </c>
       <c r="P47">
-        <v>9.433602468888886</v>
+        <v>9.253484992888886</v>
       </c>
       <c r="Q47">
-        <v>27.43360246888889</v>
+        <v>27.25348499288889</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1326262000646397</v>
+        <v>0.1340072121083854</v>
       </c>
       <c r="T47">
-        <v>1.343173700959368</v>
+        <v>1.364537518061653</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.163882678545601</v>
+        <v>2.116841750751131</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09921225453852811</v>
+        <v>0.09921539904150437</v>
       </c>
       <c r="C48">
-        <v>164.8847478295971</v>
+        <v>161.7844815090886</v>
       </c>
       <c r="D48">
-        <v>242.3407478295971</v>
+        <v>242.3264815090886</v>
       </c>
       <c r="E48">
-        <v>87.25600000000001</v>
+        <v>90.34200000000003</v>
       </c>
       <c r="F48">
-        <v>141.956</v>
+        <v>145.042</v>
       </c>
       <c r="G48">
         <v>64.5</v>
@@ -5601,28 +5601,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M48">
-        <v>10.7602648</v>
+        <v>10.9941836</v>
       </c>
       <c r="N48">
-        <v>12.01751297777777</v>
+        <v>11.78359417777777</v>
       </c>
       <c r="O48">
-        <v>2.764027984888888</v>
+        <v>2.710226660888888</v>
       </c>
       <c r="P48">
-        <v>9.253484992888886</v>
+        <v>9.073367516888885</v>
       </c>
       <c r="Q48">
-        <v>27.25348499288889</v>
+        <v>27.07336751688889</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1340072121083854</v>
+        <v>0.1354403378141592</v>
       </c>
       <c r="T48">
-        <v>1.364537518061653</v>
+        <v>1.386707516941383</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.116841750751131</v>
+        <v>2.071802564564937</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5647,22 +5647,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09921539904150437</v>
+        <v>0.09921854354448065</v>
       </c>
       <c r="C49">
-        <v>161.7844815090886</v>
+        <v>158.6842168681647</v>
       </c>
       <c r="D49">
-        <v>242.3264815090886</v>
+        <v>242.3122168681647</v>
       </c>
       <c r="E49">
-        <v>90.34200000000003</v>
+        <v>93.42800000000001</v>
       </c>
       <c r="F49">
-        <v>145.042</v>
+        <v>148.128</v>
       </c>
       <c r="G49">
         <v>64.5</v>
@@ -5683,28 +5683,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M49">
-        <v>10.9941836</v>
+        <v>11.2281024</v>
       </c>
       <c r="N49">
-        <v>11.78359417777777</v>
+        <v>11.54967537777777</v>
       </c>
       <c r="O49">
-        <v>2.710226660888888</v>
+        <v>2.656425336888888</v>
       </c>
       <c r="P49">
-        <v>9.073367516888885</v>
+        <v>8.893250040888883</v>
       </c>
       <c r="Q49">
-        <v>27.07336751688889</v>
+        <v>26.89325004088889</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1354403378141592</v>
+        <v>0.1369285837393859</v>
       </c>
       <c r="T49">
-        <v>1.386707516941383</v>
+        <v>1.409730208085717</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.071802564564937</v>
+        <v>2.028640011136501</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5729,22 +5729,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09921854354448065</v>
+        <v>0.1045793480474569</v>
       </c>
       <c r="C50">
-        <v>158.6842168681647</v>
+        <v>133.498815182657</v>
       </c>
       <c r="D50">
-        <v>242.3122168681647</v>
+        <v>220.212815182657</v>
       </c>
       <c r="E50">
-        <v>93.42800000000001</v>
+        <v>96.514</v>
       </c>
       <c r="F50">
-        <v>148.128</v>
+        <v>151.214</v>
       </c>
       <c r="G50">
         <v>64.5</v>
@@ -5765,45 +5765,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M50">
-        <v>11.2281024</v>
+        <v>13.60926</v>
       </c>
       <c r="N50">
-        <v>11.54967537777777</v>
+        <v>9.168517777777776</v>
       </c>
       <c r="O50">
-        <v>2.656425336888888</v>
+        <v>2.108759088888889</v>
       </c>
       <c r="P50">
-        <v>8.893250040888883</v>
+        <v>7.059758688888888</v>
       </c>
       <c r="Q50">
-        <v>26.89325004088889</v>
+        <v>25.05975868888889</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1369285837393859</v>
+        <v>0.1384751922499155</v>
       </c>
       <c r="T50">
-        <v>1.409730208085717</v>
+        <v>1.433655749863163</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.23</v>
       </c>
       <c r="W50">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.028640011136501</v>
+        <v>1.673697010548536</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5811,22 +5811,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1045793480474569</v>
+        <v>0.1046918325504332</v>
       </c>
       <c r="C51">
-        <v>133.498815182657</v>
+        <v>129.9922045819661</v>
       </c>
       <c r="D51">
-        <v>220.212815182657</v>
+        <v>219.792204581966</v>
       </c>
       <c r="E51">
-        <v>96.514</v>
+        <v>99.60000000000001</v>
       </c>
       <c r="F51">
-        <v>151.214</v>
+        <v>154.3</v>
       </c>
       <c r="G51">
         <v>64.5</v>
@@ -5847,28 +5847,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M51">
-        <v>13.60926</v>
+        <v>13.887</v>
       </c>
       <c r="N51">
-        <v>9.168517777777776</v>
+        <v>8.890777777777775</v>
       </c>
       <c r="O51">
-        <v>2.108759088888889</v>
+        <v>2.044878888888888</v>
       </c>
       <c r="P51">
-        <v>7.059758688888888</v>
+        <v>6.845898888888886</v>
       </c>
       <c r="Q51">
-        <v>25.05975868888889</v>
+        <v>24.84589888888889</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1384751922499155</v>
+        <v>0.1400836651008664</v>
       </c>
       <c r="T51">
-        <v>1.433655749863163</v>
+        <v>1.458538313311707</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.673697010548536</v>
+        <v>1.640223070337566</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5893,22 +5893,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1046918325504332</v>
+        <v>0.1048043170534095</v>
       </c>
       <c r="C52">
-        <v>129.9922045819661</v>
+        <v>126.4871976664537</v>
       </c>
       <c r="D52">
-        <v>219.792204581966</v>
+        <v>219.3731976664537</v>
       </c>
       <c r="E52">
-        <v>99.60000000000001</v>
+        <v>102.686</v>
       </c>
       <c r="F52">
-        <v>154.3</v>
+        <v>157.386</v>
       </c>
       <c r="G52">
         <v>64.5</v>
@@ -5929,28 +5929,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M52">
-        <v>13.887</v>
+        <v>14.16474</v>
       </c>
       <c r="N52">
-        <v>8.890777777777775</v>
+        <v>8.613037777777773</v>
       </c>
       <c r="O52">
-        <v>2.044878888888888</v>
+        <v>1.980998688888888</v>
       </c>
       <c r="P52">
-        <v>6.845898888888886</v>
+        <v>6.632039088888885</v>
       </c>
       <c r="Q52">
-        <v>24.84589888888889</v>
+        <v>24.63203908888889</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1400836651008664</v>
+        <v>0.1417577899049173</v>
       </c>
       <c r="T52">
-        <v>1.458538313311707</v>
+        <v>1.484436491594885</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.640223070337566</v>
+        <v>1.60806183366428</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5975,22 +5975,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1048043170534095</v>
+        <v>0.1049168015563857</v>
       </c>
       <c r="C53">
-        <v>126.4871976664537</v>
+        <v>122.9837852818832</v>
       </c>
       <c r="D53">
-        <v>219.3731976664537</v>
+        <v>218.9557852818832</v>
       </c>
       <c r="E53">
-        <v>102.686</v>
+        <v>105.772</v>
       </c>
       <c r="F53">
-        <v>157.386</v>
+        <v>160.472</v>
       </c>
       <c r="G53">
         <v>64.5</v>
@@ -6011,28 +6011,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M53">
-        <v>14.16474</v>
+        <v>14.44248</v>
       </c>
       <c r="N53">
-        <v>8.613037777777773</v>
+        <v>8.335297777777775</v>
       </c>
       <c r="O53">
-        <v>1.980998688888888</v>
+        <v>1.917118488888888</v>
       </c>
       <c r="P53">
-        <v>6.632039088888885</v>
+        <v>6.418179288888886</v>
       </c>
       <c r="Q53">
-        <v>24.63203908888889</v>
+        <v>24.41817928888889</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1417577899049173</v>
+        <v>0.143501669909137</v>
       </c>
       <c r="T53">
-        <v>1.484436491594885</v>
+        <v>1.511413760639862</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.60806183366428</v>
+        <v>1.577137567632275</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6057,22 +6057,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1049168015563857</v>
+        <v>0.105029286059362</v>
       </c>
       <c r="C54">
-        <v>122.9837852818832</v>
+        <v>119.4819583435587</v>
       </c>
       <c r="D54">
-        <v>218.9557852818832</v>
+        <v>218.5399583435587</v>
       </c>
       <c r="E54">
-        <v>105.772</v>
+        <v>108.858</v>
       </c>
       <c r="F54">
-        <v>160.472</v>
+        <v>163.558</v>
       </c>
       <c r="G54">
         <v>64.5</v>
@@ -6093,28 +6093,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M54">
-        <v>14.44248</v>
+        <v>14.72022</v>
       </c>
       <c r="N54">
-        <v>8.335297777777775</v>
+        <v>8.057557777777774</v>
       </c>
       <c r="O54">
-        <v>1.917118488888888</v>
+        <v>1.853238288888888</v>
       </c>
       <c r="P54">
-        <v>6.418179288888886</v>
+        <v>6.204319488888886</v>
       </c>
       <c r="Q54">
-        <v>24.41817928888889</v>
+        <v>24.20431948888889</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.143501669909137</v>
+        <v>0.1453197575731107</v>
       </c>
       <c r="T54">
-        <v>1.511413760639862</v>
+        <v>1.53953899858037</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.577137567632275</v>
+        <v>1.547380255035439</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6139,22 +6139,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.105029286059362</v>
+        <v>0.1051417705623383</v>
       </c>
       <c r="C55">
-        <v>119.4819583435587</v>
+        <v>115.9817078356655</v>
       </c>
       <c r="D55">
-        <v>218.5399583435587</v>
+        <v>218.1257078356655</v>
       </c>
       <c r="E55">
-        <v>108.858</v>
+        <v>111.944</v>
       </c>
       <c r="F55">
-        <v>163.558</v>
+        <v>166.644</v>
       </c>
       <c r="G55">
         <v>64.5</v>
@@ -6175,28 +6175,28 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M55">
-        <v>14.72022</v>
+        <v>14.99796</v>
       </c>
       <c r="N55">
-        <v>8.057557777777774</v>
+        <v>7.779817777777772</v>
       </c>
       <c r="O55">
-        <v>1.853238288888888</v>
+        <v>1.789358088888888</v>
       </c>
       <c r="P55">
-        <v>6.204319488888886</v>
+        <v>5.990459688888885</v>
       </c>
       <c r="Q55">
-        <v>24.20431948888889</v>
+        <v>23.99045968888889</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1453197575731107</v>
+        <v>0.1472168925268224</v>
       </c>
       <c r="T55">
-        <v>1.53953899858037</v>
+        <v>1.568887072953074</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.547380255035439</v>
+        <v>1.518725065127375</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6221,22 +6221,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1051417705623383</v>
+        <v>0.1314813030438243</v>
       </c>
       <c r="C56">
-        <v>115.9817078356655</v>
+        <v>45.84106507835341</v>
       </c>
       <c r="D56">
-        <v>218.1257078356655</v>
+        <v>151.0710650783534</v>
       </c>
       <c r="E56">
-        <v>111.944</v>
+        <v>115.03</v>
       </c>
       <c r="F56">
-        <v>166.644</v>
+        <v>169.73</v>
       </c>
       <c r="G56">
         <v>64.5</v>
@@ -6257,45 +6257,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M56">
-        <v>14.99796</v>
+        <v>24.91636400000001</v>
       </c>
       <c r="N56">
-        <v>7.779817777777772</v>
+        <v>-2.13858622222223</v>
       </c>
       <c r="O56">
-        <v>1.789358088888888</v>
+        <v>-0.4918748311111129</v>
       </c>
       <c r="P56">
-        <v>5.990459688888885</v>
+        <v>-1.646711391111117</v>
       </c>
       <c r="Q56">
-        <v>23.99045968888889</v>
+        <v>16.35328860888889</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1472168925268224</v>
+        <v>0.1504835818262624</v>
       </c>
       <c r="T56">
-        <v>1.568887072953074</v>
+        <v>1.619421717483718</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.23</v>
+        <v>0.2102589643051004</v>
       </c>
       <c r="W56">
-        <v>0.0693</v>
+        <v>0.1159339840400113</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.518725065127375</v>
+        <v>0.9141694100221754</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6303,22 +6303,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1314813030438243</v>
+        <v>0.1324913030438243</v>
       </c>
       <c r="C57">
-        <v>45.84106507835341</v>
+        <v>40.99500645226485</v>
       </c>
       <c r="D57">
-        <v>151.0710650783534</v>
+        <v>149.3110064522649</v>
       </c>
       <c r="E57">
-        <v>115.03</v>
+        <v>118.116</v>
       </c>
       <c r="F57">
-        <v>169.73</v>
+        <v>172.816</v>
       </c>
       <c r="G57">
         <v>64.5</v>
@@ -6339,37 +6339,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M57">
-        <v>24.91636400000001</v>
+        <v>25.36938880000001</v>
       </c>
       <c r="N57">
-        <v>-2.13858622222223</v>
+        <v>-2.591611022222231</v>
       </c>
       <c r="O57">
-        <v>-0.4918748311111129</v>
+        <v>-0.5960705351111133</v>
       </c>
       <c r="P57">
-        <v>-1.646711391111117</v>
+        <v>-1.995540487111118</v>
       </c>
       <c r="Q57">
-        <v>16.35328860888889</v>
+        <v>16.00445951288889</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1504835818262624</v>
+        <v>0.1528627541404956</v>
       </c>
       <c r="T57">
-        <v>1.619421717483718</v>
+        <v>1.656226756517439</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2102589643051004</v>
+        <v>0.2065043399425093</v>
       </c>
       <c r="W57">
-        <v>0.1159339840400113</v>
+        <v>0.1164851628964396</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9141694100221754</v>
+        <v>0.8978449562717794</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6385,22 +6385,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1324913030438243</v>
+        <v>0.1335013030438243</v>
       </c>
       <c r="C58">
-        <v>40.99500645226485</v>
+        <v>36.1894867725922</v>
       </c>
       <c r="D58">
-        <v>149.3110064522649</v>
+        <v>147.5914867725922</v>
       </c>
       <c r="E58">
-        <v>118.116</v>
+        <v>121.202</v>
       </c>
       <c r="F58">
-        <v>172.816</v>
+        <v>175.902</v>
       </c>
       <c r="G58">
         <v>64.5</v>
@@ -6421,37 +6421,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M58">
-        <v>25.36938880000001</v>
+        <v>25.82241360000001</v>
       </c>
       <c r="N58">
-        <v>-2.591611022222231</v>
+        <v>-3.044635822222233</v>
       </c>
       <c r="O58">
-        <v>-0.5960705351111133</v>
+        <v>-0.7002662391111136</v>
       </c>
       <c r="P58">
-        <v>-1.995540487111118</v>
+        <v>-2.344369583111119</v>
       </c>
       <c r="Q58">
-        <v>16.00445951288889</v>
+        <v>15.65563041688888</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1528627541404956</v>
+        <v>0.1553525856321351</v>
       </c>
       <c r="T58">
-        <v>1.656226756517439</v>
+        <v>1.694743657831799</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2065043399425093</v>
+        <v>0.2028814567856231</v>
       </c>
       <c r="W58">
-        <v>0.1164851628964396</v>
+        <v>0.1170170021438705</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8978449562717794</v>
+        <v>0.8820932903722745</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6467,22 +6467,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1335013030438243</v>
+        <v>0.1345113030438243</v>
       </c>
       <c r="C59">
-        <v>36.1894867725922</v>
+        <v>31.4231214017141</v>
       </c>
       <c r="D59">
-        <v>147.5914867725922</v>
+        <v>145.9111214017141</v>
       </c>
       <c r="E59">
-        <v>121.202</v>
+        <v>124.288</v>
       </c>
       <c r="F59">
-        <v>175.902</v>
+        <v>178.988</v>
       </c>
       <c r="G59">
         <v>64.5</v>
@@ -6503,37 +6503,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M59">
-        <v>25.82241360000001</v>
+        <v>26.27543840000001</v>
       </c>
       <c r="N59">
-        <v>-3.044635822222233</v>
+        <v>-3.497660622222231</v>
       </c>
       <c r="O59">
-        <v>-0.7002662391111136</v>
+        <v>-0.8044619431111131</v>
       </c>
       <c r="P59">
-        <v>-2.344369583111119</v>
+        <v>-2.693198679111118</v>
       </c>
       <c r="Q59">
-        <v>15.65563041688888</v>
+        <v>15.30680132088889</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1553525856321351</v>
+        <v>0.1579609805281383</v>
       </c>
       <c r="T59">
-        <v>1.694743657831799</v>
+        <v>1.735094697303984</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2028814567856231</v>
+        <v>0.1993835006341469</v>
       </c>
       <c r="W59">
-        <v>0.1170170021438705</v>
+        <v>0.1175305021069072</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8820932903722745</v>
+        <v>0.866884785365856</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6549,22 +6549,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1345113030438242</v>
+        <v>0.1355213030438243</v>
       </c>
       <c r="C60">
-        <v>31.42312140171418</v>
+        <v>26.69458804992203</v>
       </c>
       <c r="D60">
-        <v>145.9111214017142</v>
+        <v>144.268588049922</v>
       </c>
       <c r="E60">
-        <v>124.288</v>
+        <v>127.374</v>
       </c>
       <c r="F60">
-        <v>178.988</v>
+        <v>182.074</v>
       </c>
       <c r="G60">
         <v>64.5</v>
@@ -6585,37 +6585,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M60">
-        <v>26.2754384</v>
+        <v>26.7284632</v>
       </c>
       <c r="N60">
-        <v>-3.497660622222227</v>
+        <v>-3.950685422222229</v>
       </c>
       <c r="O60">
-        <v>-0.8044619431111123</v>
+        <v>-0.9086576471111126</v>
       </c>
       <c r="P60">
-        <v>-2.693198679111115</v>
+        <v>-3.042027775111116</v>
       </c>
       <c r="Q60">
-        <v>15.30680132088889</v>
+        <v>14.95797222488889</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1579609805281382</v>
+        <v>0.1606966141995562</v>
       </c>
       <c r="T60">
-        <v>1.735094697303984</v>
+        <v>1.777414080165056</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1993835006341469</v>
+        <v>0.1960041192674664</v>
       </c>
       <c r="W60">
-        <v>0.1175305021069072</v>
+        <v>0.1180265952915359</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8668847853658561</v>
+        <v>0.852191822902028</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1355213030438243</v>
+        <v>0.1365313030438243</v>
       </c>
       <c r="C61">
-        <v>26.69458804992203</v>
+        <v>22.00262330520715</v>
       </c>
       <c r="D61">
-        <v>144.268588049922</v>
+        <v>142.6626233052071</v>
       </c>
       <c r="E61">
-        <v>127.374</v>
+        <v>130.46</v>
       </c>
       <c r="F61">
-        <v>182.074</v>
+        <v>185.16</v>
       </c>
       <c r="G61">
         <v>64.5</v>
@@ -6667,37 +6667,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M61">
-        <v>26.7284632</v>
+        <v>27.181488</v>
       </c>
       <c r="N61">
-        <v>-3.950685422222229</v>
+        <v>-4.403710222222227</v>
       </c>
       <c r="O61">
-        <v>-0.9086576471111126</v>
+        <v>-1.012853351111112</v>
       </c>
       <c r="P61">
-        <v>-3.042027775111116</v>
+        <v>-3.390856871111114</v>
       </c>
       <c r="Q61">
-        <v>14.95797222488889</v>
+        <v>14.60914312888889</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1606966141995562</v>
+        <v>0.1635690295545452</v>
       </c>
       <c r="T61">
-        <v>1.777414080165056</v>
+        <v>1.821849432169183</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1960041192674664</v>
+        <v>0.192737383946342</v>
       </c>
       <c r="W61">
-        <v>0.1180265952915359</v>
+        <v>0.118506152036677</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.852191822902028</v>
+        <v>0.8379886258536609</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6713,22 +6713,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1365313030438243</v>
+        <v>0.1375413030438243</v>
       </c>
       <c r="C62">
-        <v>22.00262330520715</v>
+        <v>17.34601939227349</v>
       </c>
       <c r="D62">
-        <v>142.6626233052071</v>
+        <v>141.0920193922735</v>
       </c>
       <c r="E62">
-        <v>130.46</v>
+        <v>133.546</v>
       </c>
       <c r="F62">
-        <v>185.16</v>
+        <v>188.246</v>
       </c>
       <c r="G62">
         <v>64.5</v>
@@ -6749,37 +6749,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M62">
-        <v>27.181488</v>
+        <v>27.6345128</v>
       </c>
       <c r="N62">
-        <v>-4.403710222222227</v>
+        <v>-4.856735022222228</v>
       </c>
       <c r="O62">
-        <v>-1.012853351111112</v>
+        <v>-1.117049055111113</v>
       </c>
       <c r="P62">
-        <v>-3.390856871111114</v>
+        <v>-3.739685967111115</v>
       </c>
       <c r="Q62">
-        <v>14.60914312888889</v>
+        <v>14.26031403288889</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1635690295545452</v>
+        <v>0.166588748261072</v>
       </c>
       <c r="T62">
-        <v>1.821849432169183</v>
+        <v>1.868563520173521</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.192737383946342</v>
+        <v>0.18957775470132</v>
       </c>
       <c r="W62">
-        <v>0.118506152036677</v>
+        <v>0.1189699856098462</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8379886258536609</v>
+        <v>0.8242511073970434</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6795,22 +6795,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1375413030438243</v>
+        <v>0.1385513030438243</v>
       </c>
       <c r="C63">
-        <v>17.34601939227349</v>
+        <v>12.72362114330372</v>
       </c>
       <c r="D63">
-        <v>141.0920193922735</v>
+        <v>139.5556211433037</v>
       </c>
       <c r="E63">
-        <v>133.546</v>
+        <v>136.632</v>
       </c>
       <c r="F63">
-        <v>188.246</v>
+        <v>191.332</v>
       </c>
       <c r="G63">
         <v>64.5</v>
@@ -6831,37 +6831,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M63">
-        <v>27.6345128</v>
+        <v>28.0875376</v>
       </c>
       <c r="N63">
-        <v>-4.856735022222228</v>
+        <v>-5.30975982222223</v>
       </c>
       <c r="O63">
-        <v>-1.117049055111113</v>
+        <v>-1.221244759111113</v>
       </c>
       <c r="P63">
-        <v>-3.739685967111115</v>
+        <v>-4.088515063111116</v>
       </c>
       <c r="Q63">
-        <v>14.26031403288889</v>
+        <v>13.91148493688889</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.166588748261072</v>
+        <v>0.1697673995311002</v>
       </c>
       <c r="T63">
-        <v>1.868563520173521</v>
+        <v>1.917736244388614</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.18957775470132</v>
+        <v>0.1865200489803309</v>
       </c>
       <c r="W63">
-        <v>0.1189699856098462</v>
+        <v>0.1194188568096874</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8242511073970434</v>
+        <v>0.8109567346970912</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6877,22 +6877,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1385513030438243</v>
+        <v>0.1752378755603047</v>
       </c>
       <c r="C64">
-        <v>12.72362114330372</v>
+        <v>-29.91662364782752</v>
       </c>
       <c r="D64">
-        <v>139.5556211433037</v>
+        <v>100.0013763521725</v>
       </c>
       <c r="E64">
-        <v>136.632</v>
+        <v>139.718</v>
       </c>
       <c r="F64">
-        <v>191.332</v>
+        <v>194.418</v>
       </c>
       <c r="G64">
         <v>64.5</v>
@@ -6913,45 +6913,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M64">
-        <v>28.0875376</v>
+        <v>39.0391344</v>
       </c>
       <c r="N64">
-        <v>-5.30975982222223</v>
+        <v>-16.26135662222223</v>
       </c>
       <c r="O64">
-        <v>-1.221244759111113</v>
+        <v>-3.740112023111112</v>
       </c>
       <c r="P64">
-        <v>-4.088515063111116</v>
+        <v>-12.52124459911111</v>
       </c>
       <c r="Q64">
-        <v>13.91148493688889</v>
+        <v>5.47875540088889</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1697673995311002</v>
+        <v>0.1775950928062122</v>
       </c>
       <c r="T64">
-        <v>1.917736244388614</v>
+        <v>2.038828169849818</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1865200489803309</v>
+        <v>0.1341958260449773</v>
       </c>
       <c r="W64">
-        <v>0.1194188568096874</v>
+        <v>0.1738534781301686</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8109567346970912</v>
+        <v>0.5834601132390316</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6959,22 +6959,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1752378755603047</v>
+        <v>0.1767878755603047</v>
       </c>
       <c r="C65">
-        <v>-29.91662364782752</v>
+        <v>-34.18595556066944</v>
       </c>
       <c r="D65">
-        <v>100.0013763521725</v>
+        <v>98.81804443933058</v>
       </c>
       <c r="E65">
-        <v>139.718</v>
+        <v>142.804</v>
       </c>
       <c r="F65">
-        <v>194.418</v>
+        <v>197.504</v>
       </c>
       <c r="G65">
         <v>64.5</v>
@@ -6995,37 +6995,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M65">
-        <v>39.0391344</v>
+        <v>39.65880320000001</v>
       </c>
       <c r="N65">
-        <v>-16.26135662222223</v>
+        <v>-16.88102542222223</v>
       </c>
       <c r="O65">
-        <v>-3.740112023111112</v>
+        <v>-3.882635847111114</v>
       </c>
       <c r="P65">
-        <v>-12.52124459911111</v>
+        <v>-12.99838957511112</v>
       </c>
       <c r="Q65">
-        <v>5.47875540088889</v>
+        <v>5.001610424888884</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1775950928062122</v>
+        <v>0.1812560676063848</v>
       </c>
       <c r="T65">
-        <v>2.038828169849818</v>
+        <v>2.09546228567898</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1341958260449773</v>
+        <v>0.1320990162630245</v>
       </c>
       <c r="W65">
-        <v>0.1738534781301686</v>
+        <v>0.1742745175343847</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5834601132390316</v>
+        <v>0.5743435489696717</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7041,22 +7041,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1767878755603047</v>
+        <v>0.1783378755603047</v>
       </c>
       <c r="C66">
-        <v>-34.18595556066944</v>
+        <v>-38.4276098838842</v>
       </c>
       <c r="D66">
-        <v>98.81804443933058</v>
+        <v>97.66239011611584</v>
       </c>
       <c r="E66">
-        <v>142.804</v>
+        <v>145.89</v>
       </c>
       <c r="F66">
-        <v>197.504</v>
+        <v>200.59</v>
       </c>
       <c r="G66">
         <v>64.5</v>
@@ -7077,37 +7077,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M66">
-        <v>39.65880320000001</v>
+        <v>40.27847200000001</v>
       </c>
       <c r="N66">
-        <v>-16.88102542222223</v>
+        <v>-17.50069422222223</v>
       </c>
       <c r="O66">
-        <v>-3.882635847111114</v>
+        <v>-4.025159671111114</v>
       </c>
       <c r="P66">
-        <v>-12.99838957511112</v>
+        <v>-13.47553455111112</v>
       </c>
       <c r="Q66">
-        <v>5.001610424888884</v>
+        <v>4.524465448888884</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1812560676063848</v>
+        <v>0.1851262409665672</v>
       </c>
       <c r="T66">
-        <v>2.09546228567898</v>
+        <v>2.15533263669838</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1320990162630245</v>
+        <v>0.1300667237051318</v>
       </c>
       <c r="W66">
-        <v>0.1742745175343847</v>
+        <v>0.1746826018800095</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5743435489696717</v>
+        <v>0.5655074943701383</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7123,22 +7123,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1783378755603047</v>
+        <v>0.1798878755603047</v>
       </c>
       <c r="C67">
-        <v>-38.4276098838842</v>
+        <v>-42.64254644170066</v>
       </c>
       <c r="D67">
-        <v>97.66239011611584</v>
+        <v>96.53345355829934</v>
       </c>
       <c r="E67">
-        <v>145.89</v>
+        <v>148.976</v>
       </c>
       <c r="F67">
-        <v>200.59</v>
+        <v>203.676</v>
       </c>
       <c r="G67">
         <v>64.5</v>
@@ -7159,37 +7159,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M67">
-        <v>40.27847200000001</v>
+        <v>40.89814080000001</v>
       </c>
       <c r="N67">
-        <v>-17.50069422222223</v>
+        <v>-18.12036302222223</v>
       </c>
       <c r="O67">
-        <v>-4.025159671111114</v>
+        <v>-4.167683495111113</v>
       </c>
       <c r="P67">
-        <v>-13.47553455111112</v>
+        <v>-13.95267952711112</v>
       </c>
       <c r="Q67">
-        <v>4.524465448888884</v>
+        <v>4.047320472888885</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1851262409665672</v>
+        <v>0.1892240715832309</v>
       </c>
       <c r="T67">
-        <v>2.15533263669838</v>
+        <v>2.218724773071861</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1300667237051318</v>
+        <v>0.1280960157702056</v>
       </c>
       <c r="W67">
-        <v>0.1746826018800095</v>
+        <v>0.1750783200333427</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5655074943701383</v>
+        <v>0.5569391990008937</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7205,22 +7205,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1798878755603047</v>
+        <v>0.1814378755603047</v>
       </c>
       <c r="C68">
-        <v>-42.64254644170066</v>
+        <v>-46.83168118483403</v>
       </c>
       <c r="D68">
-        <v>96.53345355829934</v>
+        <v>95.43031881516602</v>
       </c>
       <c r="E68">
-        <v>148.976</v>
+        <v>152.062</v>
       </c>
       <c r="F68">
-        <v>203.676</v>
+        <v>206.762</v>
       </c>
       <c r="G68">
         <v>64.5</v>
@@ -7241,37 +7241,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M68">
-        <v>40.89814080000001</v>
+        <v>41.51780960000001</v>
       </c>
       <c r="N68">
-        <v>-18.12036302222223</v>
+        <v>-18.74003182222223</v>
       </c>
       <c r="O68">
-        <v>-4.167683495111113</v>
+        <v>-4.310207319111114</v>
       </c>
       <c r="P68">
-        <v>-13.95267952711112</v>
+        <v>-14.42982450311112</v>
       </c>
       <c r="Q68">
-        <v>4.047320472888885</v>
+        <v>3.570175496888886</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1892240715832309</v>
+        <v>0.1935702555706016</v>
       </c>
       <c r="T68">
-        <v>2.218724773071861</v>
+        <v>2.285958857104342</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1280960157702056</v>
+        <v>0.1261841349378144</v>
       </c>
       <c r="W68">
-        <v>0.1750783200333427</v>
+        <v>0.1754622257044869</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5569391990008937</v>
+        <v>0.5486266736426715</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7287,22 +7287,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1814378755603047</v>
+        <v>0.1829878755603047</v>
       </c>
       <c r="C69">
-        <v>-46.83168118483403</v>
+        <v>-50.99588866898216</v>
       </c>
       <c r="D69">
-        <v>95.43031881516602</v>
+        <v>94.35211133101788</v>
       </c>
       <c r="E69">
-        <v>152.062</v>
+        <v>155.148</v>
       </c>
       <c r="F69">
-        <v>206.762</v>
+        <v>209.848</v>
       </c>
       <c r="G69">
         <v>64.5</v>
@@ -7323,37 +7323,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M69">
-        <v>41.51780960000001</v>
+        <v>42.13747840000001</v>
       </c>
       <c r="N69">
-        <v>-18.74003182222223</v>
+        <v>-19.35970062222223</v>
       </c>
       <c r="O69">
-        <v>-4.310207319111114</v>
+        <v>-4.452731143111113</v>
       </c>
       <c r="P69">
-        <v>-14.42982450311112</v>
+        <v>-14.90696947911112</v>
       </c>
       <c r="Q69">
-        <v>3.570175496888886</v>
+        <v>3.093030520888885</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1935702555706016</v>
+        <v>0.1981880760571829</v>
       </c>
       <c r="T69">
-        <v>2.285958857104342</v>
+        <v>2.357395071388853</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1261841349378144</v>
+        <v>0.1243284858946113</v>
       </c>
       <c r="W69">
-        <v>0.1754622257044869</v>
+        <v>0.175834840032362</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5486266736426715</v>
+        <v>0.5405586343243969</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1829878755603047</v>
+        <v>0.1845378755603047</v>
       </c>
       <c r="C70">
-        <v>-50.99588866898216</v>
+        <v>-55.13600436718247</v>
       </c>
       <c r="D70">
-        <v>94.35211133101788</v>
+        <v>93.29799563281756</v>
       </c>
       <c r="E70">
-        <v>155.148</v>
+        <v>158.234</v>
       </c>
       <c r="F70">
-        <v>209.848</v>
+        <v>212.934</v>
       </c>
       <c r="G70">
         <v>64.5</v>
@@ -7405,37 +7405,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M70">
-        <v>42.13747840000001</v>
+        <v>42.75714720000001</v>
       </c>
       <c r="N70">
-        <v>-19.35970062222223</v>
+        <v>-19.97936942222223</v>
       </c>
       <c r="O70">
-        <v>-4.452731143111113</v>
+        <v>-4.595254967111114</v>
       </c>
       <c r="P70">
-        <v>-14.90696947911112</v>
+        <v>-15.38411445511112</v>
       </c>
       <c r="Q70">
-        <v>3.093030520888885</v>
+        <v>2.615885544888886</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1981880760571829</v>
+        <v>0.2031038204461243</v>
       </c>
       <c r="T70">
-        <v>2.357395071388853</v>
+        <v>2.433440073691719</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1243284858946113</v>
+        <v>0.1225266237801966</v>
       </c>
       <c r="W70">
-        <v>0.175834840032362</v>
+        <v>0.1761966539449365</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5405586343243969</v>
+        <v>0.5327244512182462</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7451,22 +7451,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1845378755603047</v>
+        <v>0.1860878755603047</v>
       </c>
       <c r="C71">
-        <v>-55.13600436718247</v>
+        <v>-59.25282682887627</v>
       </c>
       <c r="D71">
-        <v>93.29799563281756</v>
+        <v>92.26717317112377</v>
       </c>
       <c r="E71">
-        <v>158.234</v>
+        <v>161.3200000000001</v>
       </c>
       <c r="F71">
-        <v>212.934</v>
+        <v>216.02</v>
       </c>
       <c r="G71">
         <v>64.5</v>
@@ -7487,37 +7487,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M71">
-        <v>42.75714720000001</v>
+        <v>43.37681600000001</v>
       </c>
       <c r="N71">
-        <v>-19.97936942222223</v>
+        <v>-20.59903822222224</v>
       </c>
       <c r="O71">
-        <v>-4.595254967111114</v>
+        <v>-4.737778791111115</v>
       </c>
       <c r="P71">
-        <v>-15.38411445511112</v>
+        <v>-15.86125943111112</v>
       </c>
       <c r="Q71">
-        <v>2.615885544888886</v>
+        <v>2.138740568888881</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2031038204461243</v>
+        <v>0.2083472811276617</v>
       </c>
       <c r="T71">
-        <v>2.433440073691719</v>
+        <v>2.514554742814776</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1225266237801966</v>
+        <v>0.1207762434404795</v>
       </c>
       <c r="W71">
-        <v>0.1761966539449365</v>
+        <v>0.1765481303171517</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5327244512182462</v>
+        <v>0.5251141019151283</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7533,22 +7533,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1860878755603047</v>
+        <v>0.1876378755603047</v>
       </c>
       <c r="C72">
-        <v>-59.25282682887627</v>
+        <v>-63.34711969740871</v>
       </c>
       <c r="D72">
-        <v>92.26717317112377</v>
+        <v>91.25888030259134</v>
       </c>
       <c r="E72">
-        <v>161.3200000000001</v>
+        <v>164.4060000000001</v>
       </c>
       <c r="F72">
-        <v>216.02</v>
+        <v>219.1060000000001</v>
       </c>
       <c r="G72">
         <v>64.5</v>
@@ -7569,37 +7569,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M72">
-        <v>43.37681600000001</v>
+        <v>43.99648480000001</v>
       </c>
       <c r="N72">
-        <v>-20.59903822222224</v>
+        <v>-21.21870702222224</v>
       </c>
       <c r="O72">
-        <v>-4.737778791111115</v>
+        <v>-4.880302615111114</v>
       </c>
       <c r="P72">
-        <v>-15.86125943111112</v>
+        <v>-16.33840440711112</v>
       </c>
       <c r="Q72">
-        <v>2.138740568888881</v>
+        <v>1.661595592888883</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2083472811276617</v>
+        <v>0.2139523597872363</v>
       </c>
       <c r="T72">
-        <v>2.514554742814776</v>
+        <v>2.601263527049769</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1207762434404795</v>
+        <v>0.1190751695892052</v>
       </c>
       <c r="W72">
-        <v>0.1765481303171517</v>
+        <v>0.1768897059464876</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5251141019151283</v>
+        <v>0.517718128648718</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7615,22 +7615,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1876378755603047</v>
+        <v>0.1891878755603047</v>
       </c>
       <c r="C73">
-        <v>-63.34711969740863</v>
+        <v>-67.41961359667511</v>
       </c>
       <c r="D73">
-        <v>91.25888030259136</v>
+        <v>90.27238640332492</v>
       </c>
       <c r="E73">
-        <v>164.406</v>
+        <v>167.492</v>
       </c>
       <c r="F73">
-        <v>219.106</v>
+        <v>222.192</v>
       </c>
       <c r="G73">
         <v>64.5</v>
@@ -7651,37 +7651,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M73">
-        <v>43.9964848</v>
+        <v>44.6161536</v>
       </c>
       <c r="N73">
-        <v>-21.21870702222222</v>
+        <v>-21.83837582222223</v>
       </c>
       <c r="O73">
-        <v>-4.880302615111112</v>
+        <v>-5.022826439111113</v>
       </c>
       <c r="P73">
-        <v>-16.33840440711111</v>
+        <v>-16.81554938311112</v>
       </c>
       <c r="Q73">
-        <v>1.661595592888894</v>
+        <v>1.184450616888888</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2139523597872362</v>
+        <v>0.219957801208209</v>
       </c>
       <c r="T73">
-        <v>2.601263527049768</v>
+        <v>2.694165795872974</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1190751695892052</v>
+        <v>0.1174213477893551</v>
       </c>
       <c r="W73">
-        <v>0.1768897059464876</v>
+        <v>0.1772217933638975</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5177181286487182</v>
+        <v>0.5105275990841527</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7697,22 +7697,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1891878755603047</v>
+        <v>0.1907378755603047</v>
       </c>
       <c r="C74">
-        <v>-67.41961359667511</v>
+        <v>-71.47100789671049</v>
       </c>
       <c r="D74">
-        <v>90.27238640332492</v>
+        <v>89.30699210328955</v>
       </c>
       <c r="E74">
-        <v>167.492</v>
+        <v>170.578</v>
       </c>
       <c r="F74">
-        <v>222.192</v>
+        <v>225.278</v>
       </c>
       <c r="G74">
         <v>64.5</v>
@@ -7733,37 +7733,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M74">
-        <v>44.6161536</v>
+        <v>45.2358224</v>
       </c>
       <c r="N74">
-        <v>-21.83837582222223</v>
+        <v>-22.45804462222223</v>
       </c>
       <c r="O74">
-        <v>-5.022826439111113</v>
+        <v>-5.165350263111113</v>
       </c>
       <c r="P74">
-        <v>-16.81554938311112</v>
+        <v>-17.29269435911112</v>
       </c>
       <c r="Q74">
-        <v>1.184450616888888</v>
+        <v>0.7073056408888867</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.219957801208209</v>
+        <v>0.2264080901418463</v>
       </c>
       <c r="T74">
-        <v>2.694165795872974</v>
+        <v>2.793949714238639</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1174213477893551</v>
+        <v>0.1158128361758023</v>
       </c>
       <c r="W74">
-        <v>0.1772217933638975</v>
+        <v>0.1775447824958989</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5105275990841527</v>
+        <v>0.5035340703295752</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7779,22 +7779,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1907378755603047</v>
+        <v>0.2188563225798816</v>
       </c>
       <c r="C75">
-        <v>-71.47100789671049</v>
+        <v>-89.0677399433537</v>
       </c>
       <c r="D75">
-        <v>89.30699210328955</v>
+        <v>74.79626005664629</v>
       </c>
       <c r="E75">
-        <v>170.578</v>
+        <v>173.664</v>
       </c>
       <c r="F75">
-        <v>225.278</v>
+        <v>228.364</v>
       </c>
       <c r="G75">
         <v>64.5</v>
@@ -7815,45 +7815,45 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M75">
-        <v>45.2358224</v>
+        <v>53.8482312</v>
       </c>
       <c r="N75">
-        <v>-22.45804462222223</v>
+        <v>-31.07045342222223</v>
       </c>
       <c r="O75">
-        <v>-5.165350263111113</v>
+        <v>-7.146204287111113</v>
       </c>
       <c r="P75">
-        <v>-17.29269435911112</v>
+        <v>-23.92424913511111</v>
       </c>
       <c r="Q75">
-        <v>0.7073056408888867</v>
+        <v>-5.924249135111108</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2264080901418463</v>
+        <v>0.2359255052225977</v>
       </c>
       <c r="T75">
-        <v>2.793949714238639</v>
+        <v>2.941181098637155</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1158128361758023</v>
+        <v>0.09728989740500311</v>
       </c>
       <c r="W75">
-        <v>0.1775447824958989</v>
+        <v>0.2128590421919003</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5035340703295752</v>
+        <v>0.4229995539347962</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7861,22 +7861,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2188563225798816</v>
+        <v>0.2207563225798816</v>
       </c>
       <c r="C76">
-        <v>-89.0677399433537</v>
+        <v>-92.96601635618666</v>
       </c>
       <c r="D76">
-        <v>74.79626005664629</v>
+        <v>73.98398364381335</v>
       </c>
       <c r="E76">
-        <v>173.664</v>
+        <v>176.75</v>
       </c>
       <c r="F76">
-        <v>228.364</v>
+        <v>231.45</v>
       </c>
       <c r="G76">
         <v>64.5</v>
@@ -7897,37 +7897,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M76">
-        <v>53.8482312</v>
+        <v>54.57591000000001</v>
       </c>
       <c r="N76">
-        <v>-31.07045342222223</v>
+        <v>-31.79813222222223</v>
       </c>
       <c r="O76">
-        <v>-7.146204287111113</v>
+        <v>-7.313570411111114</v>
       </c>
       <c r="P76">
-        <v>-23.92424913511111</v>
+        <v>-24.48456181111112</v>
       </c>
       <c r="Q76">
-        <v>-5.924249135111108</v>
+        <v>-6.484561811111117</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2359255052225977</v>
+        <v>0.2435305254315016</v>
       </c>
       <c r="T76">
-        <v>2.941181098637155</v>
+        <v>3.058828342582641</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09728989740500311</v>
+        <v>0.09599269877293641</v>
       </c>
       <c r="W76">
-        <v>0.2128590421919003</v>
+        <v>0.2131649216293416</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4229995539347962</v>
+        <v>0.4173595598823322</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7943,22 +7943,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2207563225798816</v>
+        <v>0.2226563225798816</v>
       </c>
       <c r="C77">
-        <v>-92.96601635618666</v>
+        <v>-96.84683989923388</v>
       </c>
       <c r="D77">
-        <v>73.98398364381335</v>
+        <v>73.18916010076614</v>
       </c>
       <c r="E77">
-        <v>176.75</v>
+        <v>179.836</v>
       </c>
       <c r="F77">
-        <v>231.45</v>
+        <v>234.536</v>
       </c>
       <c r="G77">
         <v>64.5</v>
@@ -7979,37 +7979,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M77">
-        <v>54.57591000000001</v>
+        <v>55.30358880000001</v>
       </c>
       <c r="N77">
-        <v>-31.79813222222223</v>
+        <v>-32.52581102222223</v>
       </c>
       <c r="O77">
-        <v>-7.313570411111114</v>
+        <v>-7.480936535111113</v>
       </c>
       <c r="P77">
-        <v>-24.48456181111112</v>
+        <v>-25.04487448711112</v>
       </c>
       <c r="Q77">
-        <v>-6.484561811111117</v>
+        <v>-7.044874487111112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2435305254315016</v>
+        <v>0.2517692973244808</v>
       </c>
       <c r="T77">
-        <v>3.058828342582641</v>
+        <v>3.186279523523584</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09599269877293641</v>
+        <v>0.09472963694697673</v>
       </c>
       <c r="W77">
-        <v>0.2131649216293416</v>
+        <v>0.2134627516079029</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4173595598823322</v>
+        <v>0.4118679867259858</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8025,22 +8025,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2226563225798816</v>
+        <v>0.2245563225798816</v>
       </c>
       <c r="C78">
-        <v>-96.84683989923388</v>
+        <v>-100.7107670918753</v>
       </c>
       <c r="D78">
-        <v>73.18916010076614</v>
+        <v>72.41123290812477</v>
       </c>
       <c r="E78">
-        <v>179.836</v>
+        <v>182.922</v>
       </c>
       <c r="F78">
-        <v>234.536</v>
+        <v>237.622</v>
       </c>
       <c r="G78">
         <v>64.5</v>
@@ -8061,37 +8061,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M78">
-        <v>55.30358880000001</v>
+        <v>56.03126760000001</v>
       </c>
       <c r="N78">
-        <v>-32.52581102222223</v>
+        <v>-33.25348982222224</v>
       </c>
       <c r="O78">
-        <v>-7.480936535111113</v>
+        <v>-7.648302659111114</v>
       </c>
       <c r="P78">
-        <v>-25.04487448711112</v>
+        <v>-25.60518716311112</v>
       </c>
       <c r="Q78">
-        <v>-7.044874487111112</v>
+        <v>-7.605187163111118</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2517692973244808</v>
+        <v>0.2607244841646758</v>
       </c>
       <c r="T78">
-        <v>3.186279523523584</v>
+        <v>3.324813415850698</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09472963694697673</v>
+        <v>0.09349938192169131</v>
       </c>
       <c r="W78">
-        <v>0.2134627516079029</v>
+        <v>0.2137528457428652</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4118679867259858</v>
+        <v>0.4065190518334404</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8107,22 +8107,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2245563225798816</v>
+        <v>0.2264563225798816</v>
       </c>
       <c r="C79">
-        <v>-100.7107670918753</v>
+        <v>-104.5583310413717</v>
       </c>
       <c r="D79">
-        <v>72.41123290812477</v>
+        <v>71.64966895862837</v>
       </c>
       <c r="E79">
-        <v>182.922</v>
+        <v>186.008</v>
       </c>
       <c r="F79">
-        <v>237.622</v>
+        <v>240.708</v>
       </c>
       <c r="G79">
         <v>64.5</v>
@@ -8143,37 +8143,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M79">
-        <v>56.03126760000001</v>
+        <v>56.75894640000001</v>
       </c>
       <c r="N79">
-        <v>-33.25348982222224</v>
+        <v>-33.98116862222223</v>
       </c>
       <c r="O79">
-        <v>-7.648302659111114</v>
+        <v>-7.815668783111112</v>
       </c>
       <c r="P79">
-        <v>-25.60518716311112</v>
+        <v>-26.16549983911111</v>
       </c>
       <c r="Q79">
-        <v>-7.605187163111118</v>
+        <v>-8.16549983911111</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2607244841646758</v>
+        <v>0.2704937788994337</v>
       </c>
       <c r="T79">
-        <v>3.324813415850698</v>
+        <v>3.475941298389365</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09349938192169131</v>
+        <v>0.09230067189705424</v>
       </c>
       <c r="W79">
-        <v>0.2137528457428652</v>
+        <v>0.2140355015666746</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4065190518334404</v>
+        <v>0.4013072691176272</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8189,22 +8189,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2264563225798816</v>
+        <v>0.2283563225798816</v>
       </c>
       <c r="C80">
-        <v>-104.5583310413717</v>
+        <v>-108.3900426612025</v>
       </c>
       <c r="D80">
-        <v>71.64966895862837</v>
+        <v>70.90395733879758</v>
       </c>
       <c r="E80">
-        <v>186.008</v>
+        <v>189.0940000000001</v>
       </c>
       <c r="F80">
-        <v>240.708</v>
+        <v>243.794</v>
       </c>
       <c r="G80">
         <v>64.5</v>
@@ -8225,37 +8225,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M80">
-        <v>56.75894640000001</v>
+        <v>57.48662520000001</v>
       </c>
       <c r="N80">
-        <v>-33.98116862222223</v>
+        <v>-34.70884742222223</v>
       </c>
       <c r="O80">
-        <v>-7.815668783111112</v>
+        <v>-7.983034907111114</v>
       </c>
       <c r="P80">
-        <v>-26.16549983911111</v>
+        <v>-26.72581251511112</v>
       </c>
       <c r="Q80">
-        <v>-8.16549983911111</v>
+        <v>-8.725812515111116</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2704937788994337</v>
+        <v>0.2811934826565496</v>
       </c>
       <c r="T80">
-        <v>3.475941298389365</v>
+        <v>3.641462312598383</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09230067189705424</v>
+        <v>0.09113230896164848</v>
       </c>
       <c r="W80">
-        <v>0.2140355015666746</v>
+        <v>0.2143110015468433</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4013072691176272</v>
+        <v>0.3962274302680369</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8271,22 +8271,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2283563225798816</v>
+        <v>0.2302563225798816</v>
       </c>
       <c r="C81">
-        <v>-108.3900426612025</v>
+        <v>-112.2063918141049</v>
       </c>
       <c r="D81">
-        <v>70.90395733879758</v>
+        <v>70.17360818589515</v>
       </c>
       <c r="E81">
-        <v>189.0940000000001</v>
+        <v>192.18</v>
       </c>
       <c r="F81">
-        <v>243.794</v>
+        <v>246.88</v>
       </c>
       <c r="G81">
         <v>64.5</v>
@@ -8307,37 +8307,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M81">
-        <v>57.48662520000001</v>
+        <v>58.21430400000001</v>
       </c>
       <c r="N81">
-        <v>-34.70884742222223</v>
+        <v>-35.43652622222223</v>
       </c>
       <c r="O81">
-        <v>-7.983034907111114</v>
+        <v>-8.150401031111112</v>
       </c>
       <c r="P81">
-        <v>-26.72581251511112</v>
+        <v>-27.28612519111111</v>
       </c>
       <c r="Q81">
-        <v>-8.725812515111116</v>
+        <v>-9.286125191111111</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2811934826565496</v>
+        <v>0.2929631567893771</v>
       </c>
       <c r="T81">
-        <v>3.641462312598383</v>
+        <v>3.823535428228302</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09113230896164848</v>
+        <v>0.08999315509962789</v>
       </c>
       <c r="W81">
-        <v>0.2143110015468433</v>
+        <v>0.2145796140275077</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3962274302680369</v>
+        <v>0.3912745873896865</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8353,22 +8353,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2302563225798816</v>
+        <v>0.2321563225798816</v>
       </c>
       <c r="C82">
-        <v>-112.2063918141049</v>
+        <v>-116.0078483851909</v>
       </c>
       <c r="D82">
-        <v>70.17360818589515</v>
+        <v>69.45815161480914</v>
       </c>
       <c r="E82">
-        <v>192.18</v>
+        <v>195.266</v>
       </c>
       <c r="F82">
-        <v>246.88</v>
+        <v>249.966</v>
       </c>
       <c r="G82">
         <v>64.5</v>
@@ -8389,37 +8389,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M82">
-        <v>58.21430400000001</v>
+        <v>58.94198280000001</v>
       </c>
       <c r="N82">
-        <v>-35.43652622222223</v>
+        <v>-36.16420502222223</v>
       </c>
       <c r="O82">
-        <v>-8.150401031111112</v>
+        <v>-8.317767155111115</v>
       </c>
       <c r="P82">
-        <v>-27.28612519111111</v>
+        <v>-27.84643786711112</v>
       </c>
       <c r="Q82">
-        <v>-9.286125191111111</v>
+        <v>-9.846437867111117</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2929631567893771</v>
+        <v>0.305971743988818</v>
       </c>
       <c r="T82">
-        <v>3.823535428228302</v>
+        <v>4.02477413497716</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08999315509962789</v>
+        <v>0.08888212849345963</v>
       </c>
       <c r="W82">
-        <v>0.2145796140275077</v>
+        <v>0.2148415941012422</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3912745873896865</v>
+        <v>0.3864440369280854</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8435,22 +8435,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2321563225798816</v>
+        <v>0.2340563225798816</v>
       </c>
       <c r="C83">
-        <v>-116.0078483851909</v>
+        <v>-119.7948632900802</v>
       </c>
       <c r="D83">
-        <v>69.45815161480914</v>
+        <v>68.75713670991988</v>
       </c>
       <c r="E83">
-        <v>195.266</v>
+        <v>198.352</v>
       </c>
       <c r="F83">
-        <v>249.966</v>
+        <v>253.052</v>
       </c>
       <c r="G83">
         <v>64.5</v>
@@ -8471,37 +8471,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M83">
-        <v>58.94198280000001</v>
+        <v>59.66966160000001</v>
       </c>
       <c r="N83">
-        <v>-36.16420502222223</v>
+        <v>-36.89188382222224</v>
       </c>
       <c r="O83">
-        <v>-8.317767155111115</v>
+        <v>-8.485133279111116</v>
       </c>
       <c r="P83">
-        <v>-27.84643786711112</v>
+        <v>-28.40675054311112</v>
       </c>
       <c r="Q83">
-        <v>-9.846437867111117</v>
+        <v>-10.40675054311112</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.305971743988818</v>
+        <v>0.3204257297659746</v>
       </c>
       <c r="T83">
-        <v>4.02477413497716</v>
+        <v>4.248372698031447</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08888212849345963</v>
+        <v>0.08779820009719794</v>
       </c>
       <c r="W83">
-        <v>0.2148415941012422</v>
+        <v>0.2150971844170807</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3864440369280854</v>
+        <v>0.3817313047704257</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8517,22 +8517,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2340563225798816</v>
+        <v>0.2359563225798816</v>
       </c>
       <c r="C84">
-        <v>-119.7948632900802</v>
+        <v>-123.567869422595</v>
       </c>
       <c r="D84">
-        <v>68.75713670991988</v>
+        <v>68.07013057740504</v>
       </c>
       <c r="E84">
-        <v>198.352</v>
+        <v>201.438</v>
       </c>
       <c r="F84">
-        <v>253.052</v>
+        <v>256.138</v>
       </c>
       <c r="G84">
         <v>64.5</v>
@@ -8553,37 +8553,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M84">
-        <v>59.66966160000001</v>
+        <v>60.39734040000001</v>
       </c>
       <c r="N84">
-        <v>-36.89188382222224</v>
+        <v>-37.61956262222223</v>
       </c>
       <c r="O84">
-        <v>-8.485133279111116</v>
+        <v>-8.652499403111113</v>
       </c>
       <c r="P84">
-        <v>-28.40675054311112</v>
+        <v>-28.96706321911112</v>
       </c>
       <c r="Q84">
-        <v>-10.40675054311112</v>
+        <v>-10.96706321911111</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3204257297659746</v>
+        <v>0.3365801844580908</v>
       </c>
       <c r="T84">
-        <v>4.248372698031447</v>
+        <v>4.498276974386239</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08779820009719794</v>
+        <v>0.08674039045747266</v>
       </c>
       <c r="W84">
-        <v>0.2150971844170807</v>
+        <v>0.215346615930128</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3817313047704257</v>
+        <v>0.3771321324237942</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8599,22 +8599,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2359563225798816</v>
+        <v>0.2378563225798817</v>
       </c>
       <c r="C85">
-        <v>-123.567869422595</v>
+        <v>-127.3272825462024</v>
       </c>
       <c r="D85">
-        <v>68.07013057740504</v>
+        <v>67.39671745379762</v>
       </c>
       <c r="E85">
-        <v>201.438</v>
+        <v>204.5240000000001</v>
       </c>
       <c r="F85">
-        <v>256.138</v>
+        <v>259.224</v>
       </c>
       <c r="G85">
         <v>64.5</v>
@@ -8635,37 +8635,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M85">
-        <v>60.39734040000001</v>
+        <v>61.12501920000001</v>
       </c>
       <c r="N85">
-        <v>-37.61956262222223</v>
+        <v>-38.34724142222224</v>
       </c>
       <c r="O85">
-        <v>-8.652499403111113</v>
+        <v>-8.819865527111116</v>
       </c>
       <c r="P85">
-        <v>-28.96706321911112</v>
+        <v>-29.52737589511112</v>
       </c>
       <c r="Q85">
-        <v>-10.96706321911111</v>
+        <v>-11.52737589511112</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3365801844580908</v>
+        <v>0.3547539459867215</v>
       </c>
       <c r="T85">
-        <v>4.498276974386239</v>
+        <v>4.77941928528538</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08674039045747266</v>
+        <v>0.08570776676155036</v>
       </c>
       <c r="W85">
-        <v>0.215346615930128</v>
+        <v>0.2155901085976265</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3771321324237942</v>
+        <v>0.3726424641806536</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8681,22 +8681,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2378563225798817</v>
+        <v>0.2397563225798816</v>
       </c>
       <c r="C86">
-        <v>-127.3272825462024</v>
+        <v>-131.0735021330605</v>
       </c>
       <c r="D86">
-        <v>67.39671745379762</v>
+        <v>66.73649786693949</v>
       </c>
       <c r="E86">
-        <v>204.524</v>
+        <v>207.61</v>
       </c>
       <c r="F86">
-        <v>259.224</v>
+        <v>262.31</v>
       </c>
       <c r="G86">
         <v>64.5</v>
@@ -8717,37 +8717,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M86">
-        <v>61.1250192</v>
+        <v>61.852698</v>
       </c>
       <c r="N86">
-        <v>-38.34724142222223</v>
+        <v>-39.07492022222223</v>
       </c>
       <c r="O86">
-        <v>-8.819865527111112</v>
+        <v>-8.987231651111113</v>
       </c>
       <c r="P86">
-        <v>-29.52737589511111</v>
+        <v>-30.08768857111112</v>
       </c>
       <c r="Q86">
-        <v>-11.52737589511111</v>
+        <v>-12.08768857111112</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3547539459867213</v>
+        <v>0.3753508757191694</v>
       </c>
       <c r="T86">
-        <v>4.779419285285377</v>
+        <v>5.098047237637735</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08570776676155038</v>
+        <v>0.08469944009376743</v>
       </c>
       <c r="W86">
-        <v>0.2155901085976265</v>
+        <v>0.2158278720258897</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3726424641806537</v>
+        <v>0.3682584351902931</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8763,22 +8763,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2397563225798816</v>
+        <v>0.2416563225798816</v>
       </c>
       <c r="C87">
-        <v>-131.0735021330605</v>
+        <v>-134.8069121542278</v>
       </c>
       <c r="D87">
-        <v>66.73649786693949</v>
+        <v>66.08908784577221</v>
       </c>
       <c r="E87">
-        <v>207.61</v>
+        <v>210.696</v>
       </c>
       <c r="F87">
-        <v>262.31</v>
+        <v>265.396</v>
       </c>
       <c r="G87">
         <v>64.5</v>
@@ -8799,37 +8799,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M87">
-        <v>61.852698</v>
+        <v>62.5803768</v>
       </c>
       <c r="N87">
-        <v>-39.07492022222223</v>
+        <v>-39.80259902222222</v>
       </c>
       <c r="O87">
-        <v>-8.987231651111113</v>
+        <v>-9.154597775111112</v>
       </c>
       <c r="P87">
-        <v>-30.08768857111112</v>
+        <v>-30.64800124711111</v>
       </c>
       <c r="Q87">
-        <v>-12.08768857111112</v>
+        <v>-12.64800124711111</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3753508757191694</v>
+        <v>0.3988902239848243</v>
       </c>
       <c r="T87">
-        <v>5.098047237637735</v>
+        <v>5.462193468897573</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08469944009376743</v>
+        <v>0.08371456288337478</v>
       </c>
       <c r="W87">
-        <v>0.2158278720258897</v>
+        <v>0.2160601060721002</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3682584351902931</v>
+        <v>0.3639763603624991</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8845,22 +8845,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2416563225798816</v>
+        <v>0.2435563225798816</v>
       </c>
       <c r="C88">
-        <v>-134.8069121542278</v>
+        <v>-138.5278818243189</v>
       </c>
       <c r="D88">
-        <v>66.08908784577221</v>
+        <v>65.45411817568116</v>
       </c>
       <c r="E88">
-        <v>210.696</v>
+        <v>213.782</v>
       </c>
       <c r="F88">
-        <v>265.396</v>
+        <v>268.482</v>
       </c>
       <c r="G88">
         <v>64.5</v>
@@ -8881,37 +8881,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M88">
-        <v>62.5803768</v>
+        <v>63.30805560000001</v>
       </c>
       <c r="N88">
-        <v>-39.80259902222222</v>
+        <v>-40.53027782222223</v>
       </c>
       <c r="O88">
-        <v>-9.154597775111112</v>
+        <v>-9.321963899111113</v>
       </c>
       <c r="P88">
-        <v>-30.64800124711111</v>
+        <v>-31.20831392311112</v>
       </c>
       <c r="Q88">
-        <v>-12.64800124711111</v>
+        <v>-13.20831392311112</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3988902239848243</v>
+        <v>0.4260510104451954</v>
       </c>
       <c r="T88">
-        <v>5.462193468897573</v>
+        <v>5.882362197274309</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08371456288337478</v>
+        <v>0.08275232652839346</v>
       </c>
       <c r="W88">
-        <v>0.2160601060721002</v>
+        <v>0.2162870014046048</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3639763603624991</v>
+        <v>0.3597927240364933</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8927,22 +8927,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2435563225798816</v>
+        <v>0.2454563225798816</v>
       </c>
       <c r="C89">
-        <v>-138.5278818243189</v>
+        <v>-142.2367663036423</v>
       </c>
       <c r="D89">
-        <v>65.45411817568116</v>
+        <v>64.83123369635777</v>
       </c>
       <c r="E89">
-        <v>213.782</v>
+        <v>216.8680000000001</v>
       </c>
       <c r="F89">
-        <v>268.482</v>
+        <v>271.568</v>
       </c>
       <c r="G89">
         <v>64.5</v>
@@ -8963,37 +8963,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M89">
-        <v>63.30805560000001</v>
+        <v>64.03573440000001</v>
       </c>
       <c r="N89">
-        <v>-40.53027782222223</v>
+        <v>-41.25795662222224</v>
       </c>
       <c r="O89">
-        <v>-9.321963899111113</v>
+        <v>-9.489330023111116</v>
       </c>
       <c r="P89">
-        <v>-31.20831392311112</v>
+        <v>-31.76862659911112</v>
       </c>
       <c r="Q89">
-        <v>-13.20831392311112</v>
+        <v>-13.76862659911112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4260510104451954</v>
+        <v>0.4577385946489618</v>
       </c>
       <c r="T89">
-        <v>5.882362197274309</v>
+        <v>6.37255904704717</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08275232652839346</v>
+        <v>0.08181195918147989</v>
       </c>
       <c r="W89">
-        <v>0.2162870014046048</v>
+        <v>0.2165087400250071</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3597927240364933</v>
+        <v>0.3557041703542603</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9009,22 +9009,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2454563225798816</v>
+        <v>0.2473563225798816</v>
       </c>
       <c r="C90">
-        <v>-142.2367663036423</v>
+        <v>-145.9339073606253</v>
       </c>
       <c r="D90">
-        <v>64.83123369635777</v>
+        <v>64.22009263937474</v>
       </c>
       <c r="E90">
-        <v>216.8680000000001</v>
+        <v>219.954</v>
       </c>
       <c r="F90">
-        <v>271.568</v>
+        <v>274.654</v>
       </c>
       <c r="G90">
         <v>64.5</v>
@@ -9045,37 +9045,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M90">
-        <v>64.03573440000001</v>
+        <v>64.7634132</v>
       </c>
       <c r="N90">
-        <v>-41.25795662222224</v>
+        <v>-41.98563542222223</v>
       </c>
       <c r="O90">
-        <v>-9.489330023111116</v>
+        <v>-9.656696147111113</v>
       </c>
       <c r="P90">
-        <v>-31.76862659911112</v>
+        <v>-32.32893927511112</v>
       </c>
       <c r="Q90">
-        <v>-13.76862659911112</v>
+        <v>-14.32893927511111</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4577385946489618</v>
+        <v>0.4951875577988674</v>
       </c>
       <c r="T90">
-        <v>6.37255904704717</v>
+        <v>6.951882596778731</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08181195918147989</v>
+        <v>0.08089272368505877</v>
       </c>
       <c r="W90">
-        <v>0.2165087400250071</v>
+        <v>0.2167254957550632</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3557041703542603</v>
+        <v>0.3517074942828642</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9091,22 +9091,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2473563225798816</v>
+        <v>0.2492563225798816</v>
       </c>
       <c r="C91">
-        <v>-145.9339073606253</v>
+        <v>-149.6196339971219</v>
       </c>
       <c r="D91">
-        <v>64.22009263937474</v>
+        <v>63.62036600287809</v>
       </c>
       <c r="E91">
-        <v>219.954</v>
+        <v>223.04</v>
       </c>
       <c r="F91">
-        <v>274.654</v>
+        <v>277.74</v>
       </c>
       <c r="G91">
         <v>64.5</v>
@@ -9127,37 +9127,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M91">
-        <v>64.7634132</v>
+        <v>65.49109200000001</v>
       </c>
       <c r="N91">
-        <v>-41.98563542222223</v>
+        <v>-42.71331422222224</v>
       </c>
       <c r="O91">
-        <v>-9.656696147111113</v>
+        <v>-9.824062271111115</v>
       </c>
       <c r="P91">
-        <v>-32.32893927511112</v>
+        <v>-32.88925195111112</v>
       </c>
       <c r="Q91">
-        <v>-14.32893927511111</v>
+        <v>-14.88925195111112</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4951875577988674</v>
+        <v>0.5401263135787542</v>
       </c>
       <c r="T91">
-        <v>6.951882596778731</v>
+        <v>7.647070856456605</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08089272368505877</v>
+        <v>0.07999391564411366</v>
       </c>
       <c r="W91">
-        <v>0.2167254957550632</v>
+        <v>0.216937434691118</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3517074942828642</v>
+        <v>0.3477996332352767</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9173,22 +9173,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2492563225798816</v>
+        <v>0.2511563225798816</v>
       </c>
       <c r="C92">
-        <v>-149.6196339971219</v>
+        <v>-153.2942630390081</v>
       </c>
       <c r="D92">
-        <v>63.62036600287809</v>
+        <v>63.0317369609919</v>
       </c>
       <c r="E92">
-        <v>223.04</v>
+        <v>226.126</v>
       </c>
       <c r="F92">
-        <v>277.74</v>
+        <v>280.826</v>
       </c>
       <c r="G92">
         <v>64.5</v>
@@ -9209,37 +9209,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M92">
-        <v>65.49109200000001</v>
+        <v>66.2187708</v>
       </c>
       <c r="N92">
-        <v>-42.71331422222224</v>
+        <v>-43.44099302222223</v>
       </c>
       <c r="O92">
-        <v>-9.824062271111115</v>
+        <v>-9.991428395111113</v>
       </c>
       <c r="P92">
-        <v>-32.88925195111112</v>
+        <v>-33.44956462711112</v>
       </c>
       <c r="Q92">
-        <v>-14.88925195111112</v>
+        <v>-15.44956462711111</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5401263135787542</v>
+        <v>0.595051459531949</v>
       </c>
       <c r="T92">
-        <v>7.647070856456605</v>
+        <v>8.496745396062893</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07999391564411366</v>
+        <v>0.0791148616260465</v>
       </c>
       <c r="W92">
-        <v>0.216937434691118</v>
+        <v>0.2171447156285782</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3477996332352767</v>
+        <v>0.3439776592436804</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9255,22 +9255,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2511563225798816</v>
+        <v>0.2530563225798816</v>
       </c>
       <c r="C93">
-        <v>-153.2942630390081</v>
+        <v>-156.9580996942915</v>
       </c>
       <c r="D93">
-        <v>63.0317369609919</v>
+        <v>62.45390030570852</v>
       </c>
       <c r="E93">
-        <v>226.126</v>
+        <v>229.212</v>
       </c>
       <c r="F93">
-        <v>280.826</v>
+        <v>283.912</v>
       </c>
       <c r="G93">
         <v>64.5</v>
@@ -9291,37 +9291,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M93">
-        <v>66.2187708</v>
+        <v>66.94644960000001</v>
       </c>
       <c r="N93">
-        <v>-43.44099302222223</v>
+        <v>-44.16867182222224</v>
       </c>
       <c r="O93">
-        <v>-9.991428395111113</v>
+        <v>-10.15879451911112</v>
       </c>
       <c r="P93">
-        <v>-33.44956462711112</v>
+        <v>-34.00987730311113</v>
       </c>
       <c r="Q93">
-        <v>-15.44956462711111</v>
+        <v>-16.00987730311112</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.595051459531949</v>
+        <v>0.6637078919734428</v>
       </c>
       <c r="T93">
-        <v>8.496745396062893</v>
+        <v>9.558838570570758</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0791148616260465</v>
+        <v>0.07825491747793729</v>
       </c>
       <c r="W93">
-        <v>0.2171447156285782</v>
+        <v>0.2173474904587024</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3439776592436804</v>
+        <v>0.3402387716432055</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9337,22 +9337,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2530563225798816</v>
+        <v>0.2549563225798816</v>
       </c>
       <c r="C94">
-        <v>-156.9580996942915</v>
+        <v>-160.6114380808015</v>
       </c>
       <c r="D94">
-        <v>62.45390030570852</v>
+        <v>61.8865619191985</v>
       </c>
       <c r="E94">
-        <v>229.212</v>
+        <v>232.2980000000001</v>
       </c>
       <c r="F94">
-        <v>283.912</v>
+        <v>286.998</v>
       </c>
       <c r="G94">
         <v>64.5</v>
@@ -9373,37 +9373,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M94">
-        <v>66.94644960000001</v>
+        <v>67.67412840000001</v>
       </c>
       <c r="N94">
-        <v>-44.16867182222224</v>
+        <v>-44.89635062222224</v>
       </c>
       <c r="O94">
-        <v>-10.15879451911112</v>
+        <v>-10.32616064311112</v>
       </c>
       <c r="P94">
-        <v>-34.00987730311113</v>
+        <v>-34.57018997911113</v>
       </c>
       <c r="Q94">
-        <v>-16.00987730311112</v>
+        <v>-16.57018997911112</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6637078919734428</v>
+        <v>0.751980447969649</v>
       </c>
       <c r="T94">
-        <v>9.558838570570758</v>
+        <v>10.92438693779515</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07825491747793729</v>
+        <v>0.07741346675236806</v>
       </c>
       <c r="W94">
-        <v>0.2173474904587024</v>
+        <v>0.2175459045397916</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3402387716432055</v>
+        <v>0.3365802902276872</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9419,22 +9419,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2549563225798816</v>
+        <v>0.2568563225798817</v>
       </c>
       <c r="C95">
-        <v>-160.6114380808015</v>
+        <v>-164.2545617253774</v>
       </c>
       <c r="D95">
-        <v>61.8865619191985</v>
+        <v>61.32943827462262</v>
       </c>
       <c r="E95">
-        <v>232.2980000000001</v>
+        <v>235.3840000000001</v>
       </c>
       <c r="F95">
-        <v>286.998</v>
+        <v>290.0840000000001</v>
       </c>
       <c r="G95">
         <v>64.5</v>
@@ -9455,37 +9455,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M95">
-        <v>67.67412840000001</v>
+        <v>68.40180720000002</v>
       </c>
       <c r="N95">
-        <v>-44.89635062222224</v>
+        <v>-45.62402942222225</v>
       </c>
       <c r="O95">
-        <v>-10.32616064311112</v>
+        <v>-10.49352676711112</v>
       </c>
       <c r="P95">
-        <v>-34.57018997911113</v>
+        <v>-35.13050265511113</v>
       </c>
       <c r="Q95">
-        <v>-16.57018997911112</v>
+        <v>-17.13050265511113</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.751980447969649</v>
+        <v>0.8696771892979241</v>
       </c>
       <c r="T95">
-        <v>10.92438693779515</v>
+        <v>12.74511809409435</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07741346675236806</v>
+        <v>0.07658991923372585</v>
       </c>
       <c r="W95">
-        <v>0.2175459045397916</v>
+        <v>0.2177400970446875</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3365802902276872</v>
+        <v>0.3329996488422862</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9501,22 +9501,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2568563225798817</v>
+        <v>0.2587563225798816</v>
       </c>
       <c r="C96">
-        <v>-164.2545617253774</v>
+        <v>-167.8877440363326</v>
       </c>
       <c r="D96">
-        <v>61.32943827462262</v>
+        <v>60.78225596366745</v>
       </c>
       <c r="E96">
-        <v>235.3840000000001</v>
+        <v>238.47</v>
       </c>
       <c r="F96">
-        <v>290.0840000000001</v>
+        <v>293.17</v>
       </c>
       <c r="G96">
         <v>64.5</v>
@@ -9537,37 +9537,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M96">
-        <v>68.40180720000002</v>
+        <v>69.129486</v>
       </c>
       <c r="N96">
-        <v>-45.62402942222225</v>
+        <v>-46.35170822222223</v>
       </c>
       <c r="O96">
-        <v>-10.49352676711112</v>
+        <v>-10.66089289111111</v>
       </c>
       <c r="P96">
-        <v>-35.13050265511113</v>
+        <v>-35.69081533111112</v>
       </c>
       <c r="Q96">
-        <v>-17.13050265511113</v>
+        <v>-17.69081533111111</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8696771892979241</v>
+        <v>1.03445262715751</v>
       </c>
       <c r="T96">
-        <v>12.74511809409435</v>
+        <v>15.29414171291323</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07658991923372585</v>
+        <v>0.07578370955758139</v>
       </c>
       <c r="W96">
-        <v>0.2177400970446875</v>
+        <v>0.2179302012863223</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3329996488422862</v>
+        <v>0.3294943893807886</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9583,22 +9583,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2587563225798816</v>
+        <v>0.2606563225798816</v>
       </c>
       <c r="C97">
-        <v>-167.8877440363326</v>
+        <v>-171.5112487508519</v>
       </c>
       <c r="D97">
-        <v>60.78225596366745</v>
+        <v>60.24475124914813</v>
       </c>
       <c r="E97">
-        <v>238.47</v>
+        <v>241.556</v>
       </c>
       <c r="F97">
-        <v>293.17</v>
+        <v>296.256</v>
       </c>
       <c r="G97">
         <v>64.5</v>
@@ -9619,37 +9619,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M97">
-        <v>69.129486</v>
+        <v>69.85716480000001</v>
       </c>
       <c r="N97">
-        <v>-46.35170822222223</v>
+        <v>-47.07938702222224</v>
       </c>
       <c r="O97">
-        <v>-10.66089289111111</v>
+        <v>-10.82825901511112</v>
       </c>
       <c r="P97">
-        <v>-35.69081533111112</v>
+        <v>-36.25112800711112</v>
       </c>
       <c r="Q97">
-        <v>-17.69081533111111</v>
+        <v>-18.25112800711112</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.03445262715751</v>
+        <v>1.281615783946888</v>
       </c>
       <c r="T97">
-        <v>15.29414171291323</v>
+        <v>19.11767714114154</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07578370955758139</v>
+        <v>0.07499429591635658</v>
       </c>
       <c r="W97">
-        <v>0.2179302012863223</v>
+        <v>0.2181163450229231</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3294943893807886</v>
+        <v>0.326062156158072</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9665,22 +9665,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2606563225798816</v>
+        <v>0.2625563225798817</v>
       </c>
       <c r="C98">
-        <v>-171.5112487508519</v>
+        <v>-175.1253303588576</v>
       </c>
       <c r="D98">
-        <v>60.24475124914813</v>
+        <v>59.71666964114245</v>
       </c>
       <c r="E98">
-        <v>241.556</v>
+        <v>244.6420000000001</v>
       </c>
       <c r="F98">
-        <v>296.256</v>
+        <v>299.342</v>
       </c>
       <c r="G98">
         <v>64.5</v>
@@ -9701,37 +9701,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M98">
-        <v>69.85716480000001</v>
+        <v>70.58484360000001</v>
       </c>
       <c r="N98">
-        <v>-47.07938702222224</v>
+        <v>-47.80706582222224</v>
       </c>
       <c r="O98">
-        <v>-10.82825901511112</v>
+        <v>-10.99562513911112</v>
       </c>
       <c r="P98">
-        <v>-36.25112800711112</v>
+        <v>-36.81144068311113</v>
       </c>
       <c r="Q98">
-        <v>-18.25112800711112</v>
+        <v>-18.81144068311113</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.281615783946884</v>
+        <v>1.693554378595846</v>
       </c>
       <c r="T98">
-        <v>19.11767714114149</v>
+        <v>25.49023618818866</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07499429591635658</v>
+        <v>0.07422115884505393</v>
       </c>
       <c r="W98">
-        <v>0.2181163450229231</v>
+        <v>0.2182986507443363</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.326062156158072</v>
+        <v>0.3227006906306692</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9747,22 +9747,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2625563225798817</v>
+        <v>0.2644563225798816</v>
       </c>
       <c r="C99">
-        <v>-175.1253303588576</v>
+        <v>-178.7302345047769</v>
       </c>
       <c r="D99">
-        <v>59.71666964114245</v>
+        <v>59.19776549522313</v>
       </c>
       <c r="E99">
-        <v>244.6420000000001</v>
+        <v>247.728</v>
       </c>
       <c r="F99">
-        <v>299.342</v>
+        <v>302.428</v>
       </c>
       <c r="G99">
         <v>64.5</v>
@@ -9783,37 +9783,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M99">
-        <v>70.58484360000001</v>
+        <v>71.31252240000001</v>
       </c>
       <c r="N99">
-        <v>-47.80706582222224</v>
+        <v>-48.53474462222223</v>
       </c>
       <c r="O99">
-        <v>-10.99562513911112</v>
+        <v>-11.16299126311112</v>
       </c>
       <c r="P99">
-        <v>-36.81144068311113</v>
+        <v>-37.37175335911112</v>
       </c>
       <c r="Q99">
-        <v>-18.81144068311113</v>
+        <v>-19.37175335911111</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.693554378595846</v>
+        <v>2.517431567893768</v>
       </c>
       <c r="T99">
-        <v>25.49023618818866</v>
+        <v>38.23535428228298</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07422115884505393</v>
+        <v>0.07346380008132888</v>
       </c>
       <c r="W99">
-        <v>0.2182986507443363</v>
+        <v>0.2184772359408227</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3227006906306692</v>
+        <v>0.3194078264405603</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9829,22 +9829,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2644563225798816</v>
+        <v>0.2663563225798816</v>
       </c>
       <c r="C100">
-        <v>-178.7302345047769</v>
+        <v>-182.3261983685432</v>
       </c>
       <c r="D100">
-        <v>59.19776549522313</v>
+        <v>58.68780163145684</v>
       </c>
       <c r="E100">
-        <v>247.728</v>
+        <v>250.814</v>
       </c>
       <c r="F100">
-        <v>302.428</v>
+        <v>305.514</v>
       </c>
       <c r="G100">
         <v>64.5</v>
@@ -9865,37 +9865,37 @@
         <v>22.77777777777778</v>
       </c>
       <c r="M100">
-        <v>71.31252240000001</v>
+        <v>72.0402012</v>
       </c>
       <c r="N100">
-        <v>-48.53474462222223</v>
+        <v>-49.26242342222223</v>
       </c>
       <c r="O100">
-        <v>-11.16299126311112</v>
+        <v>-11.33035738711111</v>
       </c>
       <c r="P100">
-        <v>-37.37175335911112</v>
+        <v>-37.93206603511111</v>
       </c>
       <c r="Q100">
-        <v>-19.37175335911111</v>
+        <v>-19.93206603511111</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.517431567893768</v>
+        <v>4.989063135787537</v>
       </c>
       <c r="T100">
-        <v>38.23535428228298</v>
+        <v>76.47070856456597</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07346380008132888</v>
+        <v>0.0727217414946488</v>
       </c>
       <c r="W100">
-        <v>0.2184772359408227</v>
+        <v>0.2186522133555618</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9903,91 +9903,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3194078264405603</v>
+        <v>0.3161814847593426</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2663563225798816</v>
-      </c>
-      <c r="C101">
-        <v>-182.3261983685432</v>
-      </c>
-      <c r="D101">
-        <v>58.68780163145684</v>
-      </c>
-      <c r="E101">
-        <v>250.814</v>
-      </c>
-      <c r="F101">
-        <v>305.514</v>
-      </c>
-      <c r="G101">
-        <v>64.5</v>
-      </c>
-      <c r="H101">
-        <v>253.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.77777777777778</v>
-      </c>
-      <c r="K101">
-        <v>18</v>
-      </c>
-      <c r="L101">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="M101">
-        <v>72.0402012</v>
-      </c>
-      <c r="N101">
-        <v>-49.26242342222223</v>
-      </c>
-      <c r="O101">
-        <v>-11.33035738711111</v>
-      </c>
-      <c r="P101">
-        <v>-37.93206603511111</v>
-      </c>
-      <c r="Q101">
-        <v>-19.93206603511111</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.989063135787537</v>
-      </c>
-      <c r="T101">
-        <v>76.47070856456597</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0727217414946488</v>
-      </c>
-      <c r="W101">
-        <v>0.2186522133555618</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3161814847593426</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
